--- a/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
+++ b/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -90,12 +90,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -473,6 +473,8 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,6 +532,16 @@
           <t>Used: bolted (rule)</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs (USD)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>New pigs with no rate</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,6 +570,14 @@
       <c r="H5" t="n">
         <v>25</v>
       </c>
+      <c r="I5" s="4">
+        <f>'Crude'!L31</f>
+        <v/>
+      </c>
+      <c r="J5">
+        <f>'Crude'!D32</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -586,6 +606,14 @@
       <c r="H6" t="n">
         <v>4</v>
       </c>
+      <c r="I6" s="4">
+        <f>'HDS'!L12</f>
+        <v/>
+      </c>
+      <c r="J6">
+        <f>'HDS'!D13</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -597,22 +625,30 @@
         <v>197</v>
       </c>
       <c r="C7" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
         <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G7" t="n">
         <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="I7" s="4">
+        <f>'Coker'!L48</f>
+        <v/>
+      </c>
+      <c r="J7">
+        <f>'Coker'!D49</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -642,45 +678,69 @@
       <c r="H8" t="n">
         <v>5</v>
       </c>
+      <c r="I8" s="4">
+        <f>'Vac'!L39</f>
+        <v/>
+      </c>
+      <c r="J8">
+        <f>'Vac'!D40</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <f>SUM(B5:B8)</f>
         <v/>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="5">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="5">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
+      <c r="I9" s="6">
+        <f>SUM(I5:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="5">
+        <f>SUM(J5:J8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Costing: New pigs only, at the pigs.xlsx rate for the same size and type; used pigs are not costed (Jesse, 2026-10-02). Bolted and HR pigs without their own rate take the same-size Pin rate (pigs.xlsx prices Bolt and HR the same as Pin wherever it lists both); Foam takes the Gauge Foam rate. Sizes or types not on pigs.xlsx carry no rate and are counted in "New pigs with no rate".</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -692,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -704,10 +764,13 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Crude PR-170028 - pigs by size and type</t>
         </is>
@@ -759,6 +822,21 @@
           <t>Used: bolted (rule)</t>
         </is>
       </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rate (USD)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rate source</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs (USD)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -792,38 +870,58 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L3" s="4">
+        <f>IF(J3="","",D3*J3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>5.875"</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="C4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
+      <c r="G4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L4" s="9">
+        <f>IF(J4="","",D4*J4)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -858,38 +956,62 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="J5" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L5" s="4">
+        <f>IF(J5="","",D5*J5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>6"</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Foam</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6" t="n">
+      <c r="H6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx (Gauge Foam rate)</t>
+        </is>
+      </c>
+      <c r="L6" s="9">
+        <f>IF(J6="","",D6*J6)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -924,38 +1046,60 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="J7" s="4" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L7" s="4">
+        <f>IF(J7="","",D7*J7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>6"</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Other / unclear</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="n">
+      <c r="H8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L8" s="9">
+        <f>IF(J8="","",D8*J8)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -990,38 +1134,62 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
+      <c r="J9" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L9" s="4">
+        <f>IF(J9="","",D9*J9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>6.125"</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6" t="n">
+      <c r="C10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="n">
+      <c r="G10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L10" s="9">
+        <f>IF(J10="","",D10*J10)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1056,38 +1224,60 @@
       <c r="I11" t="n">
         <v>1</v>
       </c>
+      <c r="J11" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L11" s="4">
+        <f>IF(J11="","",D11*J11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>6.25"</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>FMJ</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L12" s="9">
+        <f>IF(J12="","",D12*J12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1122,38 +1312,60 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L13" s="4">
+        <f>IF(J13="","",D13*J13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>6.25"</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L14" s="9">
+        <f>IF(J14="","",D14*J14)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1188,38 +1400,58 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L15" s="4">
+        <f>IF(J15="","",D15*J15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>7.75"</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="n">
+      <c r="C16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="6" t="n">
+      <c r="G16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L16" s="9">
+        <f>IF(J16="","",D16*J16)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1254,38 +1486,58 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L17" s="4">
+        <f>IF(J17="","",D17*J17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>7.75"</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="n">
+      <c r="C18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="6" t="n">
+      <c r="G18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L18" s="9">
+        <f>IF(J18="","",D18*J18)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1320,38 +1572,60 @@
       <c r="I19" t="n">
         <v>3</v>
       </c>
+      <c r="J19" s="4" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L19" s="4">
+        <f>IF(J19="","",D19*J19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>8"</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>FMJ</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6" t="n">
+      <c r="C20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="6" t="n">
+      <c r="G20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L20" s="9">
+        <f>IF(J20="","",D20*J20)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1386,38 +1660,60 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L21" s="4">
+        <f>IF(J21="","",D21*J21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>8"</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L22" s="9">
+        <f>IF(J22="","",D22*J22)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1452,38 +1748,60 @@
       <c r="I23" t="n">
         <v>21</v>
       </c>
+      <c r="J23" s="4" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L23" s="4">
+        <f>IF(J23="","",D23*J23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>8.25"</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>FMJ</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="F24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="H24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L24" s="9">
+        <f>IF(J24="","",D24*J24)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1518,38 +1836,58 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L25" s="4">
+        <f>IF(J25="","",D25*J25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>8.25"</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Other / unclear</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="6" t="n">
+      <c r="F26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L26" s="9">
+        <f>IF(J26="","",D26*J26)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1584,38 +1922,62 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
+      <c r="J27" s="4" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L27" s="4">
+        <f>IF(J27="","",D27*J27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>8.5"</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Swab</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L28" s="9">
+        <f>IF(J28="","",D28*J28)</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1650,73 +2012,112 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L29" s="4">
+        <f>IF(J29="","",D29*J29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>size not legible</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Foam</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6" t="n">
+      <c r="C30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="6" t="n">
+      <c r="G30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not legible)</t>
+        </is>
+      </c>
+      <c r="L30" s="9">
+        <f>IF(J30="","",D30*J30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr"/>
-      <c r="C31" s="4">
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5">
         <f>SUM(C3:C30)</f>
         <v/>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="5">
         <f>SUM(D3:D30)</f>
         <v/>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="5">
         <f>SUM(E3:E30)</f>
         <v/>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="5">
         <f>SUM(F3:F30)</f>
         <v/>
       </c>
-      <c r="G31" s="4">
+      <c r="G31" s="5">
         <f>SUM(G3:G30)</f>
         <v/>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="5">
         <f>SUM(H3:H30)</f>
         <v/>
       </c>
-      <c r="I31" s="4">
+      <c r="I31" s="5">
         <f>SUM(I3:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="6">
+        <f>SUM(L3:L30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>New pigs with no rate</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32">
+        <f>SUMIF(J3:J30,"",D3:D30)</f>
         <v/>
       </c>
     </row>
@@ -1731,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1743,10 +2144,13 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>HDS PR-175169 - pigs by size and type</t>
         </is>
@@ -1798,6 +2202,21 @@
           <t>Used: bolted (rule)</t>
         </is>
       </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rate (USD)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rate source</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs (USD)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1831,38 +2250,62 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L3" s="4">
+        <f>IF(J3="","",D3*J3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>6"</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L4" s="9">
+        <f>IF(J4="","",D4*J4)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1897,38 +2340,60 @@
       <c r="I5" t="n">
         <v>4</v>
       </c>
+      <c r="J5" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L5" s="4">
+        <f>IF(J5="","",D5*J5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>6.25"</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>FMJ</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L6" s="9">
+        <f>IF(J6="","",D6*J6)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1963,38 +2428,58 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L7" s="4">
+        <f>IF(J7="","",D7*J7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>6.25"</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Other / unclear</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6" t="n">
+      <c r="C8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L8" s="9">
+        <f>IF(J8="","",D8*J8)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2029,38 +2514,60 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
+      <c r="J9" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L9" s="4">
+        <f>IF(J9="","",D9*J9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>6.5"</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Other / unclear</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L10" s="9">
+        <f>IF(J10="","",D10*J10)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -2095,40 +2602,69 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>no rate (size not legible)</t>
+        </is>
+      </c>
+      <c r="L11" s="4">
+        <f>IF(J11="","",D11*J11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4">
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5">
         <f>SUM(C3:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <f>SUM(D3:D11)</f>
         <v/>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <f>SUM(E3:E11)</f>
         <v/>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <f>SUM(F3:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="5">
         <f>SUM(G3:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="5">
         <f>SUM(H3:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="5">
         <f>SUM(I3:I11)</f>
+        <v/>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="6">
+        <f>SUM(L3:L11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>New pigs with no rate</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13">
+        <f>SUMIF(J3:J11,"",D3:D11)</f>
         <v/>
       </c>
     </row>
@@ -2143,7 +2679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2155,10 +2691,13 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Coker PR-170002 - pigs by size and type</t>
         </is>
@@ -2210,6 +2749,21 @@
           <t>Used: bolted (rule)</t>
         </is>
       </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rate (USD)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rate source</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs (USD)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2243,38 +2797,58 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L3" s="4">
+        <f>IF(J3="","",D3*J3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3"</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="C4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
+      <c r="G4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L4" s="9">
+        <f>IF(J4="","",D4*J4)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -2309,38 +2883,58 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L5" s="4">
+        <f>IF(J5="","",D5*J5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>3.1"</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="C6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6" t="n">
+      <c r="G6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L6" s="9">
+        <f>IF(J6="","",D6*J6)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -2375,38 +2969,58 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L7" s="4">
+        <f>IF(J7="","",D7*J7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>3.25"</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Other / unclear</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6" t="n">
+      <c r="C8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L8" s="9">
+        <f>IF(J8="","",D8*J8)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -2441,122 +3055,168 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
+      <c r="J9" s="4" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L9" s="4">
+        <f>IF(J9="","",D9*J9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>84 mm</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Honeycomb</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>3.3"</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Bolted</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="6" t="n">
+      <c r="E10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L10" s="9">
+        <f>IF(J10="","",D10*J10)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E11" t="n">
         <v>3</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
+      <c r="J11" s="4" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L11" s="4">
+        <f>IF(J11="","",D11*J11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>3.375"</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Bolted</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6" t="n">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>3.3"</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Other / unclear</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>1</v>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L12" s="9">
+        <f>IF(J12="","",D12*J12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3.375"</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -2565,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2573,56 +3233,78 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
+      <c r="J13" s="4" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L13" s="4">
+        <f>IF(J13="","",D13*J13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>3.5"</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Bolted</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" s="6" t="n">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>84 mm</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>10</v>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L14" s="9">
+        <f>IF(J14="","",D14*J14)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3.5"</t>
+          <t>3.375"</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -2631,46 +3313,66 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L15" s="4">
+        <f>IF(J15="","",D15*J15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>3.375"</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>3.5"</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Other / unclear</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="6" t="n">
-        <v>0</v>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L16" s="9">
+        <f>IF(J16="","",D16*J16)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -2681,80 +3383,104 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pin / TC / PPS</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
+        <v>10</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L17" s="4">
+        <f>IF(J17="","",D17*J17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>3.5"</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="8" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>3.6"</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Bolted</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="6" t="n">
+      <c r="G18" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>3</v>
+      <c r="J18" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L18" s="9">
+        <f>IF(J18="","",D18*J18)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3.6"</t>
+          <t>3.5"</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Other / unclear</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2763,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2771,38 +3497,60 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L19" s="4">
+        <f>IF(J19="","",D19*J19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>3.6"</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Other / unclear</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="6" t="n">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>3.5"</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Pin / TC / PPS</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0</v>
+      <c r="J20" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L20" s="9">
+        <f>IF(J20="","",D20*J20)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -2813,20 +3561,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pin / TC / PPS</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>3</v>
       </c>
       <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>3</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2835,106 +3583,146 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L21" s="4">
+        <f>IF(J21="","",D21*J21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>3.6"</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>3.625"</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Bolted</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G22" s="6" t="n">
+      <c r="F22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>3</v>
+      <c r="G22" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L22" s="9">
+        <f>IF(J22="","",D22*J22)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3.625"</t>
+          <t>3.6"</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Other / unclear</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L23" s="4">
+        <f>IF(J23="","",D23*J23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>3.625"</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Other / unclear</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="6" t="n">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>3.6"</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Pin / TC / PPS</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="6" t="n">
+      <c r="F24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="H24" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L24" s="9">
+        <f>IF(J24="","",D24*J24)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -2945,152 +3733,198 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pin / TC / PPS</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
         <v>14</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>11</v>
       </c>
-      <c r="E25" t="n">
+      <c r="I25" t="n">
         <v>3</v>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="n">
-        <v>10</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="J25" s="4" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L25" s="4">
+        <f>IF(J25="","",D25*J25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>3.625"</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I25" t="n">
+      <c r="E26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="8" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>3.7"</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Pin / TC / PPS</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>0</v>
+      <c r="J26" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L26" s="9">
+        <f>IF(J26="","",D26*J26)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3.75"</t>
+          <t>3.625"</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bolted</t>
+          <t>Other / unclear</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
       <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
         <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L27" s="4">
+        <f>IF(J27="","",D27*J27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>3.75"</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Foam</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" s="6" t="n">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>3.625"</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Pin / TC / PPS</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>0</v>
+      <c r="J28" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L28" s="9">
+        <f>IF(J28="","",D28*J28)</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3.75"</t>
+          <t>3.7"</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gauge foam</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -3101,38 +3935,60 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L29" s="4">
+        <f>IF(J29="","",D29*J29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>3.75"</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6" t="n">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Bolted</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="E30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="6" t="n">
+      <c r="G30" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="H30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L30" s="9">
+        <f>IF(J30="","",D30*J30)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -3143,14 +3999,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Other / unclear</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -3159,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -3167,49 +4023,69 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L31" s="4">
+        <f>IF(J31="","",D31*J31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>3.75"</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Pin / TC / PPS</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="6" t="n">
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Gauge foam</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="n">
+      <c r="D32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L32" s="9">
+        <f>IF(J32="","",D32*J32)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3.8"</t>
+          <t>3.75"</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -3233,44 +4109,66 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
+      <c r="J33" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L33" s="4">
+        <f>IF(J33="","",D33*J33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>3.8"</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="6" t="n">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>3.75"</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Other / unclear</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="6" t="n">
+      <c r="G34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L34" s="9">
+        <f>IF(J34="","",D34*J34)</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3.8"</t>
+          <t>3.75"</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3279,76 +4177,98 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
+      <c r="J35" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L35" s="4">
+        <f>IF(J35="","",D35*J35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>3.875"</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Bolted</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="6" t="n">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>3.8"</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Foam</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="6" t="n">
+      <c r="F36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="G36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>2</v>
+      <c r="I36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L36" s="9">
+        <f>IF(J36="","",D36*J36)</f>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3.875"</t>
+          <t>3.8"</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -3357,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -3365,122 +4285,164 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L37" s="4">
+        <f>IF(J37="","",D37*J37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>3.875"</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>3.8"</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C38" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E38" s="6" t="n">
+      <c r="C38" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H38" s="6" t="n">
+      <c r="G38" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="H38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L38" s="9">
+        <f>IF(J38="","",D38*J38)</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3.9"</t>
+          <t>3.875"</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pin / TC / PPS</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L39" s="4">
+        <f>IF(J39="","",D39*J39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>3.875"</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Foam</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I39" t="n">
+      <c r="F40" s="8" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Bolted</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D40" s="6" t="n">
+      <c r="G40" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="F40" s="6" t="n">
+      <c r="I40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>3</v>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L40" s="9">
+        <f>IF(J40="","",D40*J40)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4"</t>
+          <t>3.875"</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3489,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3497,139 +4459,335 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
+      <c r="J41" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L41" s="4">
+        <f>IF(J41="","",D41*J41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>4"</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>3.9"</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C42" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" s="6" t="n">
+      <c r="C42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L42" s="9">
+        <f>IF(J42="","",D42*J42)</f>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6.5"</t>
+          <t>4"</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Swab</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L43" s="4">
+        <f>IF(J43="","",D43*J43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Foam</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I43" t="n">
+      <c r="F44" s="8" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="G44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx (Gauge Foam rate)</t>
+        </is>
+      </c>
+      <c r="L44" s="9">
+        <f>IF(J44="","",D44*J44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pin / TC / PPS</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>16</v>
+      </c>
+      <c r="D45" t="n">
+        <v>14</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>13</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L45" s="4">
+        <f>IF(J45="","",D45*J45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>6.5"</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Swab</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L46" s="9">
+        <f>IF(J46="","",D46*J46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>size not legible</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Foam</t>
         </is>
       </c>
-      <c r="C44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="6" t="n">
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="F47" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="6" t="n">
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="I44" s="6" t="n">
+      <c r="I47" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>no rate (size not legible)</t>
+        </is>
+      </c>
+      <c r="L47" s="4">
+        <f>IF(J47="","",D47*J47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr"/>
-      <c r="C45" s="4">
-        <f>SUM(C3:C44)</f>
+      <c r="B48" s="5" t="inlineStr"/>
+      <c r="C48" s="5">
+        <f>SUM(C3:C47)</f>
         <v/>
       </c>
-      <c r="D45" s="4">
-        <f>SUM(D3:D44)</f>
+      <c r="D48" s="5">
+        <f>SUM(D3:D47)</f>
         <v/>
       </c>
-      <c r="E45" s="4">
-        <f>SUM(E3:E44)</f>
+      <c r="E48" s="5">
+        <f>SUM(E3:E47)</f>
         <v/>
       </c>
-      <c r="F45" s="4">
-        <f>SUM(F3:F44)</f>
+      <c r="F48" s="5">
+        <f>SUM(F3:F47)</f>
         <v/>
       </c>
-      <c r="G45" s="4">
-        <f>SUM(G3:G44)</f>
+      <c r="G48" s="5">
+        <f>SUM(G3:G47)</f>
         <v/>
       </c>
-      <c r="H45" s="4">
-        <f>SUM(H3:H44)</f>
+      <c r="H48" s="5">
+        <f>SUM(H3:H47)</f>
         <v/>
       </c>
-      <c r="I45" s="4">
-        <f>SUM(I3:I44)</f>
+      <c r="I48" s="5">
+        <f>SUM(I3:I47)</f>
+        <v/>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K48" s="5" t="inlineStr"/>
+      <c r="L48" s="6">
+        <f>SUM(L3:L47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>New pigs with no rate</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49">
+        <f>SUMIF(J3:J47,"",D3:D47)</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +4802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3656,10 +4814,13 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Vac PR-170029 - pigs by size and type</t>
         </is>
@@ -3711,6 +4872,21 @@
           <t>Used: bolted (rule)</t>
         </is>
       </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Rate (USD)</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Rate source</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs (USD)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3744,38 +4920,62 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L3" s="4">
+        <f>IF(J3="","",D3*J3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3.75"</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="6" t="n">
+      <c r="F4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L4" s="9">
+        <f>IF(J4="","",D4*J4)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -3810,38 +5010,60 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L5" s="4">
+        <f>IF(J5="","",D5*J5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>3.875"</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6" t="n">
+      <c r="G6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L6" s="9">
+        <f>IF(J6="","",D6*J6)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -3876,38 +5098,62 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="J7" s="4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>pigs.xlsx (Gauge Foam rate)</t>
+        </is>
+      </c>
+      <c r="L7" s="4">
+        <f>IF(J7="","",D7*J7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>4"</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Gauge foam</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6" t="n">
+      <c r="D8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L8" s="9">
+        <f>IF(J8="","",D8*J8)</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -3942,38 +5188,62 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
+      <c r="J9" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L9" s="4">
+        <f>IF(J9="","",D9*J9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>4"</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6" t="n">
+      <c r="G10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L10" s="9">
+        <f>IF(J10="","",D10*J10)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -4008,38 +5278,60 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L11" s="4">
+        <f>IF(J11="","",D11*J11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>4.125"</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L12" s="9">
+        <f>IF(J12="","",D12*J12)</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -4074,38 +5366,62 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
+      <c r="J13" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L13" s="4">
+        <f>IF(J13="","",D13*J13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>4.25"</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Bolted</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6" t="n">
+      <c r="C14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>1</v>
+      <c r="I14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L14" s="9">
+        <f>IF(J14="","",D14*J14)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -4140,38 +5456,60 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
+      <c r="J15" s="4" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L15" s="4">
+        <f>IF(J15="","",D15*J15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>5.75"</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="n">
+      <c r="C16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="6" t="n">
+      <c r="F16" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L16" s="9">
+        <f>IF(J16="","",D16*J16)</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -4206,38 +5544,58 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L17" s="4">
+        <f>IF(J17="","",D17*J17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>5.8"</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="n">
+      <c r="C18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="6" t="n">
+      <c r="F18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L18" s="9">
+        <f>IF(J18="","",D18*J18)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -4272,38 +5630,62 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
+      <c r="J19" s="4" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>pigs.xlsx (Gauge Foam rate)</t>
+        </is>
+      </c>
+      <c r="L19" s="4">
+        <f>IF(J19="","",D19*J19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>6"</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Gauge foam</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="6" t="n">
+      <c r="D20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="n">
+      <c r="G20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L20" s="9">
+        <f>IF(J20="","",D20*J20)</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -4338,38 +5720,60 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>no rate (type not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L21" s="4">
+        <f>IF(J21="","",D21*J21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>6"</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L22" s="9">
+        <f>IF(J22="","",D22*J22)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -4404,38 +5808,60 @@
       <c r="I23" t="n">
         <v>3</v>
       </c>
+      <c r="J23" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L23" s="4">
+        <f>IF(J23="","",D23*J23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>6.25"</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>Foam</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="6" t="n">
+      <c r="C24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="6" t="n">
+      <c r="E24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="G24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="n">
+      <c r="H24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L24" s="9">
+        <f>IF(J24="","",D24*J24)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -4470,38 +5896,62 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
+      <c r="J25" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L25" s="4">
+        <f>IF(J25="","",D25*J25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>8"</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="6" t="n">
+      <c r="C26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="6" t="n">
+      <c r="F26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="H26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="6" t="n">
+      <c r="I26" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L26" s="9">
+        <f>IF(J26="","",D26*J26)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -4536,38 +5986,60 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L27" s="4">
+        <f>IF(J27="","",D27*J27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>8.25"</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Bolted</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="6" t="n">
+      <c r="C28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="6" t="n">
+      <c r="E28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="6" t="n">
-        <v>1</v>
+      <c r="I28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L28" s="9">
+        <f>IF(J28="","",D28*J28)</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -4602,38 +6074,62 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
+      <c r="J29" s="4" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L29" s="4">
+        <f>IF(J29="","",D29*J29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>10"</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n">
+      <c r="C30" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E30" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="6" t="n">
+      <c r="F30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I30" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L30" s="9">
+        <f>IF(J30="","",D30*J30)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -4668,38 +6164,62 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
+      <c r="J31" s="4" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L31" s="4">
+        <f>IF(J31="","",D31*J31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>10"</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>Swab</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n">
+      <c r="C32" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="E32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="F32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="G32" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I32" s="6" t="n">
+      <c r="I32" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L32" s="9">
+        <f>IF(J32="","",D32*J32)</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -4734,38 +6254,60 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L33" s="4">
+        <f>IF(J33="","",D33*J33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>12"</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C34" s="6" t="n">
+      <c r="C34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="6" t="n">
+      <c r="D34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F34" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="6" t="n">
+      <c r="F34" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="H34" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I34" s="6" t="n">
+      <c r="I34" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>826</v>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>pigs.xlsx Pin rate, same size</t>
+        </is>
+      </c>
+      <c r="L34" s="9">
+        <f>IF(J34="","",D34*J34)</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -4800,38 +6342,60 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
+      <c r="J35" s="4" t="n">
+        <v>826</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>pigs.xlsx</t>
+        </is>
+      </c>
+      <c r="L35" s="4">
+        <f>IF(J35="","",D35*J35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>12.25"</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Pin / TC / PPS</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="6" t="n">
+      <c r="C36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="6" t="n">
+      <c r="F36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="H36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="6" t="n">
+      <c r="I36" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not on pigs.xlsx)</t>
+        </is>
+      </c>
+      <c r="L36" s="9">
+        <f>IF(J36="","",D36*J36)</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -4866,73 +6430,112 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>no rate (size not legible)</t>
+        </is>
+      </c>
+      <c r="L37" s="4">
+        <f>IF(J37="","",D37*J37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>size not legible</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Swab</t>
         </is>
       </c>
-      <c r="C38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="6" t="n">
+      <c r="C38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="6" t="n">
+      <c r="G38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>no rate (size not legible)</t>
+        </is>
+      </c>
+      <c r="L38" s="9">
+        <f>IF(J38="","",D38*J38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="4">
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5">
         <f>SUM(C3:C38)</f>
         <v/>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="5">
         <f>SUM(D3:D38)</f>
         <v/>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="5">
         <f>SUM(E3:E38)</f>
         <v/>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="5">
         <f>SUM(F3:F38)</f>
         <v/>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="5">
         <f>SUM(G3:G38)</f>
         <v/>
       </c>
-      <c r="H39" s="4">
+      <c r="H39" s="5">
         <f>SUM(H3:H38)</f>
         <v/>
       </c>
-      <c r="I39" s="4">
+      <c r="I39" s="5">
         <f>SUM(I3:I38)</f>
+        <v/>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="6">
+        <f>SUM(L3:L38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>New pigs with no rate</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40">
+        <f>SUMIF(J3:J38,"",D3:D38)</f>
         <v/>
       </c>
     </row>
@@ -4956,7 +6559,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>How the crews' written types were grouped - correct anything wrong and the counts follow.</t>
         </is>
@@ -5280,12 +6883,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5333,12 +6936,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5386,12 +6989,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5439,12 +7042,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5545,12 +7148,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5571,6 +7174,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5593,12 +7197,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5619,6 +7223,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5694,12 +7299,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5720,6 +7325,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5742,12 +7348,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5768,6 +7374,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5790,12 +7397,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5816,6 +7423,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5838,12 +7446,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5864,6 +7472,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5886,12 +7495,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5912,6 +7521,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5934,12 +7544,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5960,6 +7570,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5982,12 +7593,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6008,6 +7619,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6030,12 +7642,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6056,6 +7668,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6078,12 +7691,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6104,6 +7717,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6126,12 +7740,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6152,6 +7766,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6174,12 +7789,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6200,6 +7815,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6222,12 +7838,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6275,12 +7891,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6328,12 +7944,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6354,6 +7970,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6455,6 +8072,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6556,6 +8174,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6816,6 +8435,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6864,6 +8484,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6912,6 +8533,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6960,6 +8582,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7008,6 +8631,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7109,6 +8733,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7157,6 +8782,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7205,6 +8831,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7306,6 +8933,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7407,6 +9035,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7429,12 +9058,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7447,14 +9076,15 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Used</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>not bolted, unlabelled (rule)</t>
-        </is>
-      </c>
+          <t>bolted (rule)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7503,6 +9133,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7525,12 +9156,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7543,14 +9174,15 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Used</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>not bolted, unlabelled (rule)</t>
-        </is>
-      </c>
+          <t>bolted (rule)</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7599,6 +9231,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7621,12 +9254,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7639,14 +9272,15 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Used</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>not bolted, unlabelled (rule)</t>
-        </is>
-      </c>
+          <t>bolted (rule)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7748,6 +9382,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7796,6 +9431,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8030,12 +9666,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Other / unclear</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8083,12 +9719,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Other / unclear</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8136,12 +9772,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Other / unclear</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8189,12 +9825,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>84 mm</t>
+          <t>3.3"</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Other / unclear</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8321,6 +9957,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8475,6 +10112,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8682,6 +10320,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8836,6 +10475,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8990,6 +10630,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9091,6 +10732,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9139,6 +10781,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9293,6 +10936,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9341,6 +10985,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9389,6 +11034,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9437,6 +11083,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9750,6 +11397,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9957,6 +11605,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10005,6 +11654,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10371,6 +12021,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10790,6 +12441,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10944,6 +12596,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11045,6 +12698,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -11252,6 +12906,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11300,6 +12955,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11348,6 +13004,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11396,6 +13053,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11444,6 +13102,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11492,6 +13151,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -11805,6 +13465,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12012,6 +13673,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12113,6 +13775,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12214,6 +13877,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12315,6 +13979,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -12575,6 +14240,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -12835,6 +14501,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -13466,6 +15133,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -13620,6 +15288,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -13668,6 +15337,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -13928,6 +15598,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -14294,6 +15965,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14342,6 +16014,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14390,6 +16063,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -14438,6 +16112,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14857,6 +16532,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -14958,6 +16634,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -15059,6 +16736,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -15107,6 +16785,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -15208,6 +16887,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -15309,6 +16989,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -15728,6 +17409,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15776,6 +17458,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -16566,6 +18249,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -16667,6 +18351,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -16768,6 +18453,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -16869,6 +18555,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -17765,6 +19452,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -17813,6 +19501,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -17861,6 +19550,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -18280,6 +19970,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -18328,6 +20019,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -18376,6 +20068,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -19981,6 +21674,7 @@
           <t>2</t>
         </is>
       </c>
+      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>10.5"</t>
@@ -20062,6 +21756,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -20269,6 +21964,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -20476,6 +22172,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -20524,6 +22221,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -20731,6 +22429,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -20779,6 +22478,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -20827,6 +22527,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -20875,6 +22576,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -20923,6 +22625,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -20971,6 +22674,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -21072,6 +22776,7 @@
           <t>bolted (rule)</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -21544,6 +23249,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -21698,6 +23404,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -22276,6 +23983,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -27730,6 +29438,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -27778,6 +29487,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -27826,6 +29536,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -27874,6 +29585,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -27922,6 +29634,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -28076,6 +29789,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -28124,6 +29838,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -28225,6 +29940,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -28326,6 +30042,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -28480,6 +30197,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -28528,6 +30246,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -28576,6 +30295,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -28677,6 +30397,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -28778,6 +30499,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -28879,6 +30601,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -28980,6 +30703,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -29134,6 +30858,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -29235,6 +30960,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -29442,6 +31168,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -29543,6 +31270,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -29591,6 +31319,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -29639,6 +31368,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -29687,6 +31417,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -29735,6 +31466,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -29909,6 +31641,7 @@
           <t>3</t>
         </is>
       </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
           <t>10"</t>
@@ -29990,6 +31723,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -30356,6 +32090,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -30404,6 +32139,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -30929,6 +32665,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -31030,6 +32767,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -31078,6 +32816,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -31285,6 +33024,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -31333,6 +33073,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -31540,6 +33281,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -31800,6 +33542,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -32007,6 +33750,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -32055,6 +33799,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -32209,6 +33954,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -32257,6 +34003,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -32305,6 +34052,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -32353,6 +34101,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -32401,6 +34150,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -32449,6 +34199,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -32550,6 +34301,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -32651,6 +34403,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -32699,6 +34452,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -32747,6 +34501,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -32795,6 +34550,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -32843,6 +34599,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -32891,6 +34648,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -32939,6 +34697,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -32987,6 +34746,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -33088,6 +34848,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -33242,6 +35003,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -33290,6 +35052,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -33338,6 +35101,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -33386,6 +35150,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -33646,6 +35411,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -33694,6 +35460,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -33742,6 +35509,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -33790,6 +35558,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -33838,6 +35607,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -33939,6 +35709,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -34040,6 +35811,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -34088,6 +35860,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -34454,6 +36227,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -34502,6 +36276,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -34550,6 +36325,7 @@
           <t>not bolted, unlabelled (rule)</t>
         </is>
       </c>
+      <c r="K571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -34598,6 +36374,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -34646,6 +36423,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -34747,6 +36525,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -34795,6 +36574,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K576" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -34843,6 +36623,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -34891,6 +36672,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K578" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -34992,6 +36774,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -35040,6 +36823,7 @@
           <t>labelled</t>
         </is>
       </c>
+      <c r="K581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -35117,7 +36901,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Pipeline Pigging Specialties Ltd. - invoice 09302026-1, Sept 30, 2026, "Lima". Kept separate.</t>
         </is>
@@ -35144,12 +36928,12 @@
           <t>Amount (USD)</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Qty x unit price</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Amount / (qty x unit)</t>
         </is>
@@ -35174,7 +36958,7 @@
         <f>B3*C3</f>
         <v/>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="10">
         <f>D3/E3</f>
         <v/>
       </c>
@@ -35198,7 +36982,7 @@
         <f>B4*C4</f>
         <v/>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="10">
         <f>D4/E4</f>
         <v/>
       </c>
@@ -35222,7 +37006,7 @@
         <f>B5*C5</f>
         <v/>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="10">
         <f>D5/E5</f>
         <v/>
       </c>
@@ -35246,7 +37030,7 @@
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="10">
         <f>D6/E6</f>
         <v/>
       </c>
@@ -35270,7 +37054,7 @@
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="10">
         <f>D7/E7</f>
         <v/>
       </c>
@@ -35294,7 +37078,7 @@
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="10">
         <f>D8/E8</f>
         <v/>
       </c>
@@ -35318,7 +37102,7 @@
         <f>B9*C9</f>
         <v/>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="10">
         <f>D9/E9</f>
         <v/>
       </c>
@@ -35342,7 +37126,7 @@
         <f>B10*C10</f>
         <v/>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="10">
         <f>D10/E10</f>
         <v/>
       </c>
@@ -35366,7 +37150,7 @@
         <f>B11*C11</f>
         <v/>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="10">
         <f>D11/E11</f>
         <v/>
       </c>
@@ -35390,7 +37174,7 @@
         <f>B12*C12</f>
         <v/>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="10">
         <f>D12/E12</f>
         <v/>
       </c>
@@ -35414,7 +37198,7 @@
         <f>B13*C13</f>
         <v/>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="10">
         <f>D13/E13</f>
         <v/>
       </c>
@@ -35438,7 +37222,7 @@
         <f>B14*C14</f>
         <v/>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="10">
         <f>D14/E14</f>
         <v/>
       </c>
@@ -35462,7 +37246,7 @@
         <f>B15*C15</f>
         <v/>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="10">
         <f>D15/E15</f>
         <v/>
       </c>
@@ -35486,7 +37270,7 @@
         <f>B16*C16</f>
         <v/>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="10">
         <f>D16/E16</f>
         <v/>
       </c>
@@ -35510,7 +37294,7 @@
         <f>B17*C17</f>
         <v/>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="10">
         <f>D17/E17</f>
         <v/>
       </c>
@@ -35534,7 +37318,7 @@
         <f>B18*C18</f>
         <v/>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="10">
         <f>D18/E18</f>
         <v/>
       </c>
@@ -35558,7 +37342,7 @@
         <f>B19*C19</f>
         <v/>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="10">
         <f>D19/E19</f>
         <v/>
       </c>
@@ -35582,7 +37366,7 @@
         <f>B20*C20</f>
         <v/>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="10">
         <f>D20/E20</f>
         <v/>
       </c>
@@ -35606,7 +37390,7 @@
         <f>B21*C21</f>
         <v/>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="10">
         <f>D21/E21</f>
         <v/>
       </c>
@@ -35630,7 +37414,7 @@
         <f>B22*C22</f>
         <v/>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="10">
         <f>D22/E22</f>
         <v/>
       </c>
@@ -35654,7 +37438,7 @@
         <f>B23*C23</f>
         <v/>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="10">
         <f>D23/E23</f>
         <v/>
       </c>
@@ -35678,7 +37462,7 @@
         <f>B24*C24</f>
         <v/>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="10">
         <f>D24/E24</f>
         <v/>
       </c>
@@ -35702,7 +37486,7 @@
         <f>B25*C25</f>
         <v/>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="10">
         <f>D25/E25</f>
         <v/>
       </c>
@@ -35726,7 +37510,7 @@
         <f>B26*C26</f>
         <v/>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="10">
         <f>D26/E26</f>
         <v/>
       </c>
@@ -35750,7 +37534,7 @@
         <f>B27*C27</f>
         <v/>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="10">
         <f>D27/E27</f>
         <v/>
       </c>
@@ -35774,7 +37558,7 @@
         <f>B28*C28</f>
         <v/>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="10">
         <f>D28/E28</f>
         <v/>
       </c>
@@ -35798,7 +37582,7 @@
         <f>B29*C29</f>
         <v/>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="10">
         <f>D29/E29</f>
         <v/>
       </c>
@@ -35822,7 +37606,7 @@
         <f>B30*C30</f>
         <v/>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="10">
         <f>D30/E30</f>
         <v/>
       </c>
@@ -35846,7 +37630,7 @@
         <f>B31*C31</f>
         <v/>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="10">
         <f>D31/E31</f>
         <v/>
       </c>
@@ -35870,7 +37654,7 @@
         <f>B32*C32</f>
         <v/>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="10">
         <f>D32/E32</f>
         <v/>
       </c>
@@ -35894,7 +37678,7 @@
         <f>B33*C33</f>
         <v/>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="10">
         <f>D33/E33</f>
         <v/>
       </c>
@@ -35918,7 +37702,7 @@
         <f>B34*C34</f>
         <v/>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="10">
         <f>D34/E34</f>
         <v/>
       </c>
@@ -35942,7 +37726,7 @@
         <f>B35*C35</f>
         <v/>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="10">
         <f>D35/E35</f>
         <v/>
       </c>
@@ -35966,52 +37750,52 @@
         <f>B36*C36</f>
         <v/>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="10">
         <f>D36/E36</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="B37" s="4">
+      <c r="B37" s="5">
         <f>SUM(B3:B36)</f>
         <v/>
       </c>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4">
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5">
         <f>SUM(D3:D36)</f>
         <v/>
       </c>
-      <c r="E37" s="4">
+      <c r="E37" s="5">
         <f>SUM(E3:E36)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>7% markup</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n">
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n">
         <v>3845.89</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Total (invoice)</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n">
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n">
         <v>58787.19</v>
       </c>
     </row>
@@ -36046,7 +37830,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>pigs.xlsx (Sheet1; Sheet2 is identical) - line list with rates. Kept separate.</t>
         </is>
@@ -37771,17 +39555,17 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B109" s="4">
+      <c r="B109" s="5">
         <f>SUM(B3:B108)</f>
         <v/>
       </c>
-      <c r="C109" s="4" t="n"/>
-      <c r="D109" s="4">
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5">
         <f>SUM(D3:D108)</f>
         <v/>
       </c>

--- a/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
+++ b/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -475,6 +475,8 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,6 +544,16 @@
           <t>New pigs with no rate</t>
         </is>
       </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>New pigs still with no rate</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,6 +590,14 @@
         <f>'Crude'!D32</f>
         <v/>
       </c>
+      <c r="K5" s="4">
+        <f>'Crude'!N31</f>
+        <v/>
+      </c>
+      <c r="L5">
+        <f>'Crude'!N32</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -614,6 +634,14 @@
         <f>'HDS'!D13</f>
         <v/>
       </c>
+      <c r="K6" s="4">
+        <f>'HDS'!N12</f>
+        <v/>
+      </c>
+      <c r="L6">
+        <f>'HDS'!N13</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -650,6 +678,14 @@
         <f>'Coker'!D49</f>
         <v/>
       </c>
+      <c r="K7" s="4">
+        <f>'Coker'!N48</f>
+        <v/>
+      </c>
+      <c r="L7">
+        <f>'Coker'!N49</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -686,6 +722,14 @@
         <f>'Vac'!D40</f>
         <v/>
       </c>
+      <c r="K8" s="4">
+        <f>'Vac'!N39</f>
+        <v/>
+      </c>
+      <c r="L8">
+        <f>'Vac'!N40</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -729,18 +773,26 @@
         <f>SUM(J5:J8)</f>
         <v/>
       </c>
+      <c r="K9" s="6">
+        <f>SUM(K5:K8)</f>
+        <v/>
+      </c>
+      <c r="L9" s="5">
+        <f>SUM(L5:L8)</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Costing: New pigs only, at the pigs.xlsx rate for the same size and type; used pigs are not costed (Jesse, 2026-10-02). Bolted and HR pigs without their own rate take the same-size Pin rate (pigs.xlsx prices Bolt and HR the same as Pin wherever it lists both); Foam takes the Gauge Foam rate. Sizes or types not on pigs.xlsx carry no rate and are counted in "New pigs with no rate".</t>
+          <t>Costing: New pigs only, at the pigs.xlsx rate for the same size and type; used pigs are not costed (Jesse, 2026-10-02). Bolted and HR pigs without their own rate take the same-size Pin rate (pigs.xlsx prices Bolt and HR the same as Pin wherever it lists both); Foam takes the Gauge Foam rate. Sizes or types not on pigs.xlsx carry no rate and are counted in "New pigs with no rate". Second view (Jesse, 2026-10-02: admin may count them as Pin): rated pigs unchanged; unrated Pin/HR/FMJ/unclear pigs take the same-size Pin rate where pigs.xlsx has one. Foams, swabs and honeycomb are not repriced. Neither view is treated as the correct one.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A11:L11"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -752,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -767,6 +819,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -837,6 +891,16 @@
           <t>Cost - new pigs (USD)</t>
         </is>
       </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Rate - unrated pigs at Pin (USD)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -880,6 +944,11 @@
         <f>IF(J3="","",D3*J3)</f>
         <v/>
       </c>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4">
+        <f>IF(M3="","",D3*M3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -923,6 +992,11 @@
         <f>IF(J4="","",D4*J4)</f>
         <v/>
       </c>
+      <c r="M4" s="9" t="n"/>
+      <c r="N4" s="9">
+        <f>IF(M4="","",D4*M4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -968,6 +1042,13 @@
         <f>IF(J5="","",D5*J5)</f>
         <v/>
       </c>
+      <c r="M5" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="N5" s="4">
+        <f>IF(M5="","",D5*M5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -1013,6 +1094,13 @@
         <f>IF(J6="","",D6*J6)</f>
         <v/>
       </c>
+      <c r="M6" s="9" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="N6" s="9">
+        <f>IF(M6="","",D6*M6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1058,6 +1146,13 @@
         <f>IF(J7="","",D7*J7)</f>
         <v/>
       </c>
+      <c r="M7" s="4" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="N7" s="4">
+        <f>IF(M7="","",D7*M7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1101,6 +1196,13 @@
         <f>IF(J8="","",D8*J8)</f>
         <v/>
       </c>
+      <c r="M8" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(M8="","",D8*M8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1146,6 +1248,13 @@
         <f>IF(J9="","",D9*J9)</f>
         <v/>
       </c>
+      <c r="M9" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="N9" s="4">
+        <f>IF(M9="","",D9*M9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1191,6 +1300,13 @@
         <f>IF(J10="","",D10*J10)</f>
         <v/>
       </c>
+      <c r="M10" s="9" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N10" s="9">
+        <f>IF(M10="","",D10*M10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1236,6 +1352,13 @@
         <f>IF(J11="","",D11*J11)</f>
         <v/>
       </c>
+      <c r="M11" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N11" s="4">
+        <f>IF(M11="","",D11*M11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -1279,6 +1402,13 @@
         <f>IF(J12="","",D12*J12)</f>
         <v/>
       </c>
+      <c r="M12" s="9" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N12" s="9">
+        <f>IF(M12="","",D12*M12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1322,6 +1452,13 @@
         <f>IF(J13="","",D13*J13)</f>
         <v/>
       </c>
+      <c r="M13" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N13" s="4">
+        <f>IF(M13="","",D13*M13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1367,6 +1504,13 @@
         <f>IF(J14="","",D14*J14)</f>
         <v/>
       </c>
+      <c r="M14" s="9" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N14" s="9">
+        <f>IF(M14="","",D14*M14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1410,6 +1554,11 @@
         <f>IF(J15="","",D15*J15)</f>
         <v/>
       </c>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4">
+        <f>IF(M15="","",D15*M15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1453,6 +1602,11 @@
         <f>IF(J16="","",D16*J16)</f>
         <v/>
       </c>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9">
+        <f>IF(M16="","",D16*M16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1496,6 +1650,11 @@
         <f>IF(J17="","",D17*J17)</f>
         <v/>
       </c>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4">
+        <f>IF(M17="","",D17*M17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1539,6 +1698,11 @@
         <f>IF(J18="","",D18*J18)</f>
         <v/>
       </c>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="9">
+        <f>IF(M18="","",D18*M18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1584,6 +1748,13 @@
         <f>IF(J19="","",D19*J19)</f>
         <v/>
       </c>
+      <c r="M19" s="4" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="N19" s="4">
+        <f>IF(M19="","",D19*M19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1627,6 +1798,13 @@
         <f>IF(J20="","",D20*J20)</f>
         <v/>
       </c>
+      <c r="M20" s="9" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="N20" s="9">
+        <f>IF(M20="","",D20*M20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1670,6 +1848,13 @@
         <f>IF(J21="","",D21*J21)</f>
         <v/>
       </c>
+      <c r="M21" s="4" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="N21" s="4">
+        <f>IF(M21="","",D21*M21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -1715,6 +1900,13 @@
         <f>IF(J22="","",D22*J22)</f>
         <v/>
       </c>
+      <c r="M22" s="9" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="N22" s="9">
+        <f>IF(M22="","",D22*M22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1760,6 +1952,13 @@
         <f>IF(J23="","",D23*J23)</f>
         <v/>
       </c>
+      <c r="M23" s="4" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="N23" s="4">
+        <f>IF(M23="","",D23*M23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1803,6 +2002,13 @@
         <f>IF(J24="","",D24*J24)</f>
         <v/>
       </c>
+      <c r="M24" s="9" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="N24" s="9">
+        <f>IF(M24="","",D24*M24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1846,6 +2052,11 @@
         <f>IF(J25="","",D25*J25)</f>
         <v/>
       </c>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4">
+        <f>IF(M25="","",D25*M25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -1889,6 +2100,13 @@
         <f>IF(J26="","",D26*J26)</f>
         <v/>
       </c>
+      <c r="M26" s="9" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="N26" s="9">
+        <f>IF(M26="","",D26*M26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1934,6 +2152,13 @@
         <f>IF(J27="","",D27*J27)</f>
         <v/>
       </c>
+      <c r="M27" s="4" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="N27" s="4">
+        <f>IF(M27="","",D27*M27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -1979,6 +2204,13 @@
         <f>IF(J28="","",D28*J28)</f>
         <v/>
       </c>
+      <c r="M28" s="9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="N28" s="9">
+        <f>IF(M28="","",D28*M28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2022,6 +2254,11 @@
         <f>IF(J29="","",D29*J29)</f>
         <v/>
       </c>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4">
+        <f>IF(M29="","",D29*M29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -2063,6 +2300,11 @@
       </c>
       <c r="L30" s="9">
         <f>IF(J30="","",D30*J30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="9" t="n"/>
+      <c r="N30" s="9">
+        <f>IF(M30="","",D30*M30)</f>
         <v/>
       </c>
     </row>
@@ -2107,6 +2349,11 @@
         <f>SUM(L3:L30)</f>
         <v/>
       </c>
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="6">
+        <f>SUM(N3:N30)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2118,6 +2365,19 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32">
         <f>SUMIF(J3:J30,"",D3:D30)</f>
+        <v/>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32">
+        <f>SUMIF(M3:M30,"",D3:D30)</f>
         <v/>
       </c>
     </row>
@@ -2132,7 +2392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2147,6 +2407,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2217,6 +2479,16 @@
           <t>Cost - new pigs (USD)</t>
         </is>
       </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Rate - unrated pigs at Pin (USD)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2262,6 +2534,13 @@
         <f>IF(J3="","",D3*J3)</f>
         <v/>
       </c>
+      <c r="M3" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="N3" s="4">
+        <f>IF(M3="","",D3*M3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -2307,6 +2586,13 @@
         <f>IF(J4="","",D4*J4)</f>
         <v/>
       </c>
+      <c r="M4" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="N4" s="9">
+        <f>IF(M4="","",D4*M4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2352,6 +2638,13 @@
         <f>IF(J5="","",D5*J5)</f>
         <v/>
       </c>
+      <c r="M5" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N5" s="4">
+        <f>IF(M5="","",D5*M5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -2395,6 +2688,13 @@
         <f>IF(J6="","",D6*J6)</f>
         <v/>
       </c>
+      <c r="M6" s="9" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N6" s="9">
+        <f>IF(M6="","",D6*M6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2438,6 +2738,11 @@
         <f>IF(J7="","",D7*J7)</f>
         <v/>
       </c>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4">
+        <f>IF(M7="","",D7*M7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -2481,6 +2786,13 @@
         <f>IF(J8="","",D8*J8)</f>
         <v/>
       </c>
+      <c r="M8" s="9" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(M8="","",D8*M8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2526,6 +2838,13 @@
         <f>IF(J9="","",D9*J9)</f>
         <v/>
       </c>
+      <c r="M9" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N9" s="4">
+        <f>IF(M9="","",D9*M9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -2569,6 +2888,11 @@
         <f>IF(J10="","",D10*J10)</f>
         <v/>
       </c>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="9">
+        <f>IF(M10="","",D10*M10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2610,6 +2934,11 @@
       </c>
       <c r="L11" s="4">
         <f>IF(J11="","",D11*J11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4">
+        <f>IF(M11="","",D11*M11)</f>
         <v/>
       </c>
     </row>
@@ -2654,6 +2983,11 @@
         <f>SUM(L3:L11)</f>
         <v/>
       </c>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="6">
+        <f>SUM(N3:N11)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2665,6 +2999,19 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13">
         <f>SUMIF(J3:J11,"",D3:D11)</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13">
+        <f>SUMIF(M3:M11,"",D3:D11)</f>
         <v/>
       </c>
     </row>
@@ -2679,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2694,6 +3041,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2764,6 +3113,16 @@
           <t>Cost - new pigs (USD)</t>
         </is>
       </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Rate - unrated pigs at Pin (USD)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2807,6 +3166,11 @@
         <f>IF(J3="","",D3*J3)</f>
         <v/>
       </c>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4">
+        <f>IF(M3="","",D3*M3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -2850,6 +3214,11 @@
         <f>IF(J4="","",D4*J4)</f>
         <v/>
       </c>
+      <c r="M4" s="9" t="n"/>
+      <c r="N4" s="9">
+        <f>IF(M4="","",D4*M4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2893,6 +3262,11 @@
         <f>IF(J5="","",D5*J5)</f>
         <v/>
       </c>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4">
+        <f>IF(M5="","",D5*M5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -2936,6 +3310,11 @@
         <f>IF(J6="","",D6*J6)</f>
         <v/>
       </c>
+      <c r="M6" s="9" t="n"/>
+      <c r="N6" s="9">
+        <f>IF(M6="","",D6*M6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2979,6 +3358,11 @@
         <f>IF(J7="","",D7*J7)</f>
         <v/>
       </c>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4">
+        <f>IF(M7="","",D7*M7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -3022,6 +3406,13 @@
         <f>IF(J8="","",D8*J8)</f>
         <v/>
       </c>
+      <c r="M8" s="9" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(M8="","",D8*M8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3067,6 +3458,13 @@
         <f>IF(J9="","",D9*J9)</f>
         <v/>
       </c>
+      <c r="M9" s="4" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="N9" s="4">
+        <f>IF(M9="","",D9*M9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -3112,6 +3510,13 @@
         <f>IF(J10="","",D10*J10)</f>
         <v/>
       </c>
+      <c r="M10" s="9" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="N10" s="9">
+        <f>IF(M10="","",D10*M10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3157,6 +3562,13 @@
         <f>IF(J11="","",D11*J11)</f>
         <v/>
       </c>
+      <c r="M11" s="4" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="N11" s="4">
+        <f>IF(M11="","",D11*M11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -3200,6 +3612,13 @@
         <f>IF(J12="","",D12*J12)</f>
         <v/>
       </c>
+      <c r="M12" s="9" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="N12" s="9">
+        <f>IF(M12="","",D12*M12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3245,6 +3664,13 @@
         <f>IF(J13="","",D13*J13)</f>
         <v/>
       </c>
+      <c r="M13" s="4" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="N13" s="4">
+        <f>IF(M13="","",D13*M13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -3288,6 +3714,11 @@
         <f>IF(J14="","",D14*J14)</f>
         <v/>
       </c>
+      <c r="M14" s="9" t="n"/>
+      <c r="N14" s="9">
+        <f>IF(M14="","",D14*M14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3331,6 +3762,11 @@
         <f>IF(J15="","",D15*J15)</f>
         <v/>
       </c>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4">
+        <f>IF(M15="","",D15*M15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -3374,6 +3810,11 @@
         <f>IF(J16="","",D16*J16)</f>
         <v/>
       </c>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9">
+        <f>IF(M16="","",D16*M16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3419,6 +3860,13 @@
         <f>IF(J17="","",D17*J17)</f>
         <v/>
       </c>
+      <c r="M17" s="4" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N17" s="4">
+        <f>IF(M17="","",D17*M17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -3464,6 +3912,13 @@
         <f>IF(J18="","",D18*J18)</f>
         <v/>
       </c>
+      <c r="M18" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N18" s="9">
+        <f>IF(M18="","",D18*M18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3507,6 +3962,13 @@
         <f>IF(J19="","",D19*J19)</f>
         <v/>
       </c>
+      <c r="M19" s="4" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N19" s="4">
+        <f>IF(M19="","",D19*M19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -3552,6 +4014,13 @@
         <f>IF(J20="","",D20*J20)</f>
         <v/>
       </c>
+      <c r="M20" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N20" s="9">
+        <f>IF(M20="","",D20*M20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3595,6 +4064,11 @@
         <f>IF(J21="","",D21*J21)</f>
         <v/>
       </c>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4">
+        <f>IF(M21="","",D21*M21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -3638,6 +4112,11 @@
         <f>IF(J22="","",D22*J22)</f>
         <v/>
       </c>
+      <c r="M22" s="9" t="n"/>
+      <c r="N22" s="9">
+        <f>IF(M22="","",D22*M22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3681,6 +4160,11 @@
         <f>IF(J23="","",D23*J23)</f>
         <v/>
       </c>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4">
+        <f>IF(M23="","",D23*M23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -3724,6 +4208,11 @@
         <f>IF(J24="","",D24*J24)</f>
         <v/>
       </c>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9">
+        <f>IF(M24="","",D24*M24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3769,6 +4258,13 @@
         <f>IF(J25="","",D25*J25)</f>
         <v/>
       </c>
+      <c r="M25" s="4" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N25" s="4">
+        <f>IF(M25="","",D25*M25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -3814,6 +4310,13 @@
         <f>IF(J26="","",D26*J26)</f>
         <v/>
       </c>
+      <c r="M26" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N26" s="9">
+        <f>IF(M26="","",D26*M26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3857,6 +4360,13 @@
         <f>IF(J27="","",D27*J27)</f>
         <v/>
       </c>
+      <c r="M27" s="4" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N27" s="4">
+        <f>IF(M27="","",D27*M27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -3902,6 +4412,13 @@
         <f>IF(J28="","",D28*J28)</f>
         <v/>
       </c>
+      <c r="M28" s="9" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="N28" s="9">
+        <f>IF(M28="","",D28*M28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3945,6 +4462,11 @@
         <f>IF(J29="","",D29*J29)</f>
         <v/>
       </c>
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4">
+        <f>IF(M29="","",D29*M29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -3990,6 +4512,13 @@
         <f>IF(J30="","",D30*J30)</f>
         <v/>
       </c>
+      <c r="M30" s="9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="N30" s="9">
+        <f>IF(M30="","",D30*M30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4033,6 +4562,11 @@
         <f>IF(J31="","",D31*J31)</f>
         <v/>
       </c>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4">
+        <f>IF(M31="","",D31*M31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -4076,6 +4610,11 @@
         <f>IF(J32="","",D32*J32)</f>
         <v/>
       </c>
+      <c r="M32" s="9" t="n"/>
+      <c r="N32" s="9">
+        <f>IF(M32="","",D32*M32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4121,6 +4660,13 @@
         <f>IF(J33="","",D33*J33)</f>
         <v/>
       </c>
+      <c r="M33" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="N33" s="4">
+        <f>IF(M33="","",D33*M33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -4164,6 +4710,13 @@
         <f>IF(J34="","",D34*J34)</f>
         <v/>
       </c>
+      <c r="M34" s="9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="N34" s="9">
+        <f>IF(M34="","",D34*M34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4209,6 +4762,13 @@
         <f>IF(J35="","",D35*J35)</f>
         <v/>
       </c>
+      <c r="M35" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="N35" s="4">
+        <f>IF(M35="","",D35*M35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -4252,6 +4812,11 @@
         <f>IF(J36="","",D36*J36)</f>
         <v/>
       </c>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="9">
+        <f>IF(M36="","",D36*M36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4295,6 +4860,11 @@
         <f>IF(J37="","",D37*J37)</f>
         <v/>
       </c>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4">
+        <f>IF(M37="","",D37*M37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -4338,6 +4908,11 @@
         <f>IF(J38="","",D38*J38)</f>
         <v/>
       </c>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="9">
+        <f>IF(M38="","",D38*M38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4383,6 +4958,13 @@
         <f>IF(J39="","",D39*J39)</f>
         <v/>
       </c>
+      <c r="M39" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="N39" s="4">
+        <f>IF(M39="","",D39*M39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -4426,6 +5008,11 @@
         <f>IF(J40="","",D40*J40)</f>
         <v/>
       </c>
+      <c r="M40" s="9" t="n"/>
+      <c r="N40" s="9">
+        <f>IF(M40="","",D40*M40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4471,6 +5058,13 @@
         <f>IF(J41="","",D41*J41)</f>
         <v/>
       </c>
+      <c r="M41" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="N41" s="4">
+        <f>IF(M41="","",D41*M41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -4514,6 +5108,11 @@
         <f>IF(J42="","",D42*J42)</f>
         <v/>
       </c>
+      <c r="M42" s="9" t="n"/>
+      <c r="N42" s="9">
+        <f>IF(M42="","",D42*M42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4559,6 +5158,13 @@
         <f>IF(J43="","",D43*J43)</f>
         <v/>
       </c>
+      <c r="M43" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="N43" s="4">
+        <f>IF(M43="","",D43*M43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -4604,6 +5210,13 @@
         <f>IF(J44="","",D44*J44)</f>
         <v/>
       </c>
+      <c r="M44" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N44" s="9">
+        <f>IF(M44="","",D44*M44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4649,6 +5262,13 @@
         <f>IF(J45="","",D45*J45)</f>
         <v/>
       </c>
+      <c r="M45" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="N45" s="4">
+        <f>IF(M45="","",D45*M45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -4692,6 +5312,11 @@
         <f>IF(J46="","",D46*J46)</f>
         <v/>
       </c>
+      <c r="M46" s="9" t="n"/>
+      <c r="N46" s="9">
+        <f>IF(M46="","",D46*M46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4733,6 +5358,11 @@
       </c>
       <c r="L47" s="4">
         <f>IF(J47="","",D47*J47)</f>
+        <v/>
+      </c>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4">
+        <f>IF(M47="","",D47*M47)</f>
         <v/>
       </c>
     </row>
@@ -4777,6 +5407,11 @@
         <f>SUM(L3:L47)</f>
         <v/>
       </c>
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="6">
+        <f>SUM(N3:N47)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4788,6 +5423,19 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49">
         <f>SUMIF(J3:J47,"",D3:D47)</f>
+        <v/>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49">
+        <f>SUMIF(M3:M47,"",D3:D47)</f>
         <v/>
       </c>
     </row>
@@ -4802,7 +5450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4817,6 +5465,8 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4887,6 +5537,16 @@
           <t>Cost - new pigs (USD)</t>
         </is>
       </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Rate - unrated pigs at Pin (USD)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4932,6 +5592,13 @@
         <f>IF(J3="","",D3*J3)</f>
         <v/>
       </c>
+      <c r="M3" s="4" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="N3" s="4">
+        <f>IF(M3="","",D3*M3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -4977,6 +5644,13 @@
         <f>IF(J4="","",D4*J4)</f>
         <v/>
       </c>
+      <c r="M4" s="9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="N4" s="9">
+        <f>IF(M4="","",D4*M4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5020,6 +5694,11 @@
         <f>IF(J5="","",D5*J5)</f>
         <v/>
       </c>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4">
+        <f>IF(M5="","",D5*M5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -5065,6 +5744,13 @@
         <f>IF(J6="","",D6*J6)</f>
         <v/>
       </c>
+      <c r="M6" s="9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="N6" s="9">
+        <f>IF(M6="","",D6*M6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5110,6 +5796,13 @@
         <f>IF(J7="","",D7*J7)</f>
         <v/>
       </c>
+      <c r="M7" s="4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N7" s="4">
+        <f>IF(M7="","",D7*M7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -5155,6 +5848,13 @@
         <f>IF(J8="","",D8*J8)</f>
         <v/>
       </c>
+      <c r="M8" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N8" s="9">
+        <f>IF(M8="","",D8*M8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5200,6 +5900,13 @@
         <f>IF(J9="","",D9*J9)</f>
         <v/>
       </c>
+      <c r="M9" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="N9" s="4">
+        <f>IF(M9="","",D9*M9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -5245,6 +5952,13 @@
         <f>IF(J10="","",D10*J10)</f>
         <v/>
       </c>
+      <c r="M10" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="N10" s="9">
+        <f>IF(M10="","",D10*M10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5288,6 +6002,11 @@
         <f>IF(J11="","",D11*J11)</f>
         <v/>
       </c>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4">
+        <f>IF(M11="","",D11*M11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -5333,6 +6052,13 @@
         <f>IF(J12="","",D12*J12)</f>
         <v/>
       </c>
+      <c r="M12" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="N12" s="9">
+        <f>IF(M12="","",D12*M12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5378,6 +6104,13 @@
         <f>IF(J13="","",D13*J13)</f>
         <v/>
       </c>
+      <c r="M13" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="N13" s="4">
+        <f>IF(M13="","",D13*M13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -5423,6 +6156,13 @@
         <f>IF(J14="","",D14*J14)</f>
         <v/>
       </c>
+      <c r="M14" s="9" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="N14" s="9">
+        <f>IF(M14="","",D14*M14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5468,6 +6208,13 @@
         <f>IF(J15="","",D15*J15)</f>
         <v/>
       </c>
+      <c r="M15" s="4" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="N15" s="4">
+        <f>IF(M15="","",D15*M15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -5511,6 +6258,11 @@
         <f>IF(J16="","",D16*J16)</f>
         <v/>
       </c>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9">
+        <f>IF(M16="","",D16*M16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5554,6 +6306,11 @@
         <f>IF(J17="","",D17*J17)</f>
         <v/>
       </c>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4">
+        <f>IF(M17="","",D17*M17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -5597,6 +6354,11 @@
         <f>IF(J18="","",D18*J18)</f>
         <v/>
       </c>
+      <c r="M18" s="9" t="n"/>
+      <c r="N18" s="9">
+        <f>IF(M18="","",D18*M18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5642,6 +6404,13 @@
         <f>IF(J19="","",D19*J19)</f>
         <v/>
       </c>
+      <c r="M19" s="4" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="N19" s="4">
+        <f>IF(M19="","",D19*M19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -5687,6 +6456,13 @@
         <f>IF(J20="","",D20*J20)</f>
         <v/>
       </c>
+      <c r="M20" s="9" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="N20" s="9">
+        <f>IF(M20="","",D20*M20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5730,6 +6506,13 @@
         <f>IF(J21="","",D21*J21)</f>
         <v/>
       </c>
+      <c r="M21" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="N21" s="4">
+        <f>IF(M21="","",D21*M21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -5775,6 +6558,13 @@
         <f>IF(J22="","",D22*J22)</f>
         <v/>
       </c>
+      <c r="M22" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="N22" s="9">
+        <f>IF(M22="","",D22*M22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5820,6 +6610,13 @@
         <f>IF(J23="","",D23*J23)</f>
         <v/>
       </c>
+      <c r="M23" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N23" s="4">
+        <f>IF(M23="","",D23*M23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -5863,6 +6660,11 @@
         <f>IF(J24="","",D24*J24)</f>
         <v/>
       </c>
+      <c r="M24" s="9" t="n"/>
+      <c r="N24" s="9">
+        <f>IF(M24="","",D24*M24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5908,6 +6710,13 @@
         <f>IF(J25="","",D25*J25)</f>
         <v/>
       </c>
+      <c r="M25" s="4" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="N25" s="4">
+        <f>IF(M25="","",D25*M25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -5953,6 +6762,13 @@
         <f>IF(J26="","",D26*J26)</f>
         <v/>
       </c>
+      <c r="M26" s="9" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="N26" s="9">
+        <f>IF(M26="","",D26*M26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5996,6 +6812,11 @@
         <f>IF(J27="","",D27*J27)</f>
         <v/>
       </c>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4">
+        <f>IF(M27="","",D27*M27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -6041,6 +6862,13 @@
         <f>IF(J28="","",D28*J28)</f>
         <v/>
       </c>
+      <c r="M28" s="9" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="N28" s="9">
+        <f>IF(M28="","",D28*M28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6086,6 +6914,13 @@
         <f>IF(J29="","",D29*J29)</f>
         <v/>
       </c>
+      <c r="M29" s="4" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="N29" s="4">
+        <f>IF(M29="","",D29*M29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -6131,6 +6966,13 @@
         <f>IF(J30="","",D30*J30)</f>
         <v/>
       </c>
+      <c r="M30" s="9" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="N30" s="9">
+        <f>IF(M30="","",D30*M30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6176,6 +7018,13 @@
         <f>IF(J31="","",D31*J31)</f>
         <v/>
       </c>
+      <c r="M31" s="4" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="N31" s="4">
+        <f>IF(M31="","",D31*M31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -6221,6 +7070,13 @@
         <f>IF(J32="","",D32*J32)</f>
         <v/>
       </c>
+      <c r="M32" s="9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="N32" s="9">
+        <f>IF(M32="","",D32*M32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6264,6 +7120,11 @@
         <f>IF(J33="","",D33*J33)</f>
         <v/>
       </c>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4">
+        <f>IF(M33="","",D33*M33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -6309,6 +7170,13 @@
         <f>IF(J34="","",D34*J34)</f>
         <v/>
       </c>
+      <c r="M34" s="9" t="n">
+        <v>826</v>
+      </c>
+      <c r="N34" s="9">
+        <f>IF(M34="","",D34*M34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6354,6 +7222,13 @@
         <f>IF(J35="","",D35*J35)</f>
         <v/>
       </c>
+      <c r="M35" s="4" t="n">
+        <v>826</v>
+      </c>
+      <c r="N35" s="4">
+        <f>IF(M35="","",D35*M35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -6397,6 +7272,11 @@
         <f>IF(J36="","",D36*J36)</f>
         <v/>
       </c>
+      <c r="M36" s="9" t="n"/>
+      <c r="N36" s="9">
+        <f>IF(M36="","",D36*M36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6440,6 +7320,11 @@
         <f>IF(J37="","",D37*J37)</f>
         <v/>
       </c>
+      <c r="M37" s="4" t="n"/>
+      <c r="N37" s="4">
+        <f>IF(M37="","",D37*M37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -6481,6 +7366,11 @@
       </c>
       <c r="L38" s="9">
         <f>IF(J38="","",D38*J38)</f>
+        <v/>
+      </c>
+      <c r="M38" s="9" t="n"/>
+      <c r="N38" s="9">
+        <f>IF(M38="","",D38*M38)</f>
         <v/>
       </c>
     </row>
@@ -6525,6 +7415,11 @@
         <f>SUM(L3:L38)</f>
         <v/>
       </c>
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="6">
+        <f>SUM(N3:N38)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6536,6 +7431,19 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40">
         <f>SUMIF(J3:J38,"",D3:D38)</f>
+        <v/>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40">
+        <f>SUMIF(M3:M38,"",D3:D38)</f>
         <v/>
       </c>
     </row>

--- a/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
+++ b/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -475,8 +475,6 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,16 +542,6 @@
           <t>New pigs with no rate</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>New pigs still with no rate</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -590,14 +578,6 @@
         <f>'Crude'!D32</f>
         <v/>
       </c>
-      <c r="K5" s="4">
-        <f>'Crude'!N31</f>
-        <v/>
-      </c>
-      <c r="L5">
-        <f>'Crude'!N32</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -634,14 +614,6 @@
         <f>'HDS'!D13</f>
         <v/>
       </c>
-      <c r="K6" s="4">
-        <f>'HDS'!N12</f>
-        <v/>
-      </c>
-      <c r="L6">
-        <f>'HDS'!N13</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -678,14 +650,6 @@
         <f>'Coker'!D49</f>
         <v/>
       </c>
-      <c r="K7" s="4">
-        <f>'Coker'!N48</f>
-        <v/>
-      </c>
-      <c r="L7">
-        <f>'Coker'!N49</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -722,14 +686,6 @@
         <f>'Vac'!D40</f>
         <v/>
       </c>
-      <c r="K8" s="4">
-        <f>'Vac'!N39</f>
-        <v/>
-      </c>
-      <c r="L8">
-        <f>'Vac'!N40</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -773,26 +729,18 @@
         <f>SUM(J5:J8)</f>
         <v/>
       </c>
-      <c r="K9" s="6">
-        <f>SUM(K5:K8)</f>
-        <v/>
-      </c>
-      <c r="L9" s="5">
-        <f>SUM(L5:L8)</f>
-        <v/>
-      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Costing: New pigs only, at the pigs.xlsx rate for the same size and type; used pigs are not costed (Jesse, 2026-10-02). Bolted and HR pigs without their own rate take the same-size Pin rate (pigs.xlsx prices Bolt and HR the same as Pin wherever it lists both); Foam takes the Gauge Foam rate. Sizes or types not on pigs.xlsx carry no rate and are counted in "New pigs with no rate". Second view (Jesse, 2026-10-02: admin may count them as Pin): rated pigs unchanged; unrated Pin/HR/FMJ/unclear pigs take the same-size Pin rate where pigs.xlsx has one. Foams, swabs and honeycomb are not repriced. Neither view is treated as the correct one.</t>
+          <t>Costing: New pigs only; used pigs are not costed (Jesse, 2026-10-02). Rates are from pigs.xlsx for the same size and type. Any pig without its own rate is priced as Pin at the same size (Jesse, 2026-10-02: "Unrated are priced as PIN"). Foam takes the Gauge Foam rate; foams, swabs and honeycomb are not repriced as Pin. Sizes not on pigs.xlsx at all carry no rate and are counted in "New pigs with no rate".</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A11:L11"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -804,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -817,10 +765,8 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -891,16 +837,6 @@
           <t>Cost - new pigs (USD)</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Rate - unrated pigs at Pin (USD)</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -944,11 +880,6 @@
         <f>IF(J3="","",D3*J3)</f>
         <v/>
       </c>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4">
-        <f>IF(M3="","",D3*M3)</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -992,11 +923,6 @@
         <f>IF(J4="","",D4*J4)</f>
         <v/>
       </c>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="9">
-        <f>IF(M4="","",D4*M4)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1035,20 +961,13 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L5" s="4">
         <f>IF(J5="","",D5*J5)</f>
         <v/>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="N5" s="4">
-        <f>IF(M5="","",D5*M5)</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -1094,13 +1013,6 @@
         <f>IF(J6="","",D6*J6)</f>
         <v/>
       </c>
-      <c r="M6" s="9" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="N6" s="9">
-        <f>IF(M6="","",D6*M6)</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1146,13 +1058,6 @@
         <f>IF(J7="","",D7*J7)</f>
         <v/>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="N7" s="4">
-        <f>IF(M7="","",D7*M7)</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1186,23 +1091,18 @@
       <c r="I8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="9" t="n"/>
+      <c r="J8" s="9" t="n">
+        <v>118</v>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L8" s="9">
         <f>IF(J8="","",D8*J8)</f>
         <v/>
       </c>
-      <c r="M8" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="N8" s="9">
-        <f>IF(M8="","",D8*M8)</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1248,13 +1148,6 @@
         <f>IF(J9="","",D9*J9)</f>
         <v/>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="N9" s="4">
-        <f>IF(M9="","",D9*M9)</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1293,20 +1186,13 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L10" s="9">
         <f>IF(J10="","",D10*J10)</f>
         <v/>
       </c>
-      <c r="M10" s="9" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N10" s="9">
-        <f>IF(M10="","",D10*M10)</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1352,13 +1238,6 @@
         <f>IF(J11="","",D11*J11)</f>
         <v/>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N11" s="4">
-        <f>IF(M11="","",D11*M11)</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -1392,23 +1271,18 @@
       <c r="I12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="9" t="n"/>
+      <c r="J12" s="9" t="n">
+        <v>129.8</v>
+      </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L12" s="9">
         <f>IF(J12="","",D12*J12)</f>
         <v/>
       </c>
-      <c r="M12" s="9" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N12" s="9">
-        <f>IF(M12="","",D12*M12)</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1442,23 +1316,18 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="n"/>
+      <c r="J13" s="4" t="n">
+        <v>129.8</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L13" s="4">
         <f>IF(J13="","",D13*J13)</f>
         <v/>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N13" s="4">
-        <f>IF(M13="","",D13*M13)</f>
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1504,13 +1373,6 @@
         <f>IF(J14="","",D14*J14)</f>
         <v/>
       </c>
-      <c r="M14" s="9" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N14" s="9">
-        <f>IF(M14="","",D14*M14)</f>
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1554,11 +1416,6 @@
         <f>IF(J15="","",D15*J15)</f>
         <v/>
       </c>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4">
-        <f>IF(M15="","",D15*M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1602,11 +1459,6 @@
         <f>IF(J16="","",D16*J16)</f>
         <v/>
       </c>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9">
-        <f>IF(M16="","",D16*M16)</f>
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1643,18 +1495,13 @@
       <c r="J17" s="4" t="n"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>no rate (size not on pigs.xlsx)</t>
         </is>
       </c>
       <c r="L17" s="4">
         <f>IF(J17="","",D17*J17)</f>
         <v/>
       </c>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4">
-        <f>IF(M17="","",D17*M17)</f>
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -1698,11 +1545,6 @@
         <f>IF(J18="","",D18*J18)</f>
         <v/>
       </c>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="9">
-        <f>IF(M18="","",D18*M18)</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1748,13 +1590,6 @@
         <f>IF(J19="","",D19*J19)</f>
         <v/>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="N19" s="4">
-        <f>IF(M19="","",D19*M19)</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1788,23 +1623,18 @@
       <c r="I20" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="9" t="n"/>
+      <c r="J20" s="9" t="n">
+        <v>230.1</v>
+      </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L20" s="9">
         <f>IF(J20="","",D20*J20)</f>
         <v/>
       </c>
-      <c r="M20" s="9" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="N20" s="9">
-        <f>IF(M20="","",D20*M20)</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1838,23 +1668,18 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="4" t="n"/>
+      <c r="J21" s="4" t="n">
+        <v>230.1</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L21" s="4">
         <f>IF(J21="","",D21*J21)</f>
         <v/>
       </c>
-      <c r="M21" s="4" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="N21" s="4">
-        <f>IF(M21="","",D21*M21)</f>
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -1900,13 +1725,6 @@
         <f>IF(J22="","",D22*J22)</f>
         <v/>
       </c>
-      <c r="M22" s="9" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="N22" s="9">
-        <f>IF(M22="","",D22*M22)</f>
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1952,13 +1770,6 @@
         <f>IF(J23="","",D23*J23)</f>
         <v/>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="N23" s="4">
-        <f>IF(M23="","",D23*M23)</f>
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -1992,23 +1803,18 @@
       <c r="I24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="9" t="n"/>
+      <c r="J24" s="9" t="n">
+        <v>247.8</v>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L24" s="9">
         <f>IF(J24="","",D24*J24)</f>
         <v/>
       </c>
-      <c r="M24" s="9" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="N24" s="9">
-        <f>IF(M24="","",D24*M24)</f>
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2052,11 +1858,6 @@
         <f>IF(J25="","",D25*J25)</f>
         <v/>
       </c>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4">
-        <f>IF(M25="","",D25*M25)</f>
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -2090,23 +1891,18 @@
       <c r="I26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="9" t="n"/>
+      <c r="J26" s="9" t="n">
+        <v>247.8</v>
+      </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L26" s="9">
         <f>IF(J26="","",D26*J26)</f>
         <v/>
       </c>
-      <c r="M26" s="9" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="N26" s="9">
-        <f>IF(M26="","",D26*M26)</f>
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2152,13 +1948,6 @@
         <f>IF(J27="","",D27*J27)</f>
         <v/>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="N27" s="4">
-        <f>IF(M27="","",D27*M27)</f>
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -2204,13 +1993,6 @@
         <f>IF(J28="","",D28*J28)</f>
         <v/>
       </c>
-      <c r="M28" s="9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="N28" s="9">
-        <f>IF(M28="","",D28*M28)</f>
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2254,11 +2036,6 @@
         <f>IF(J29="","",D29*J29)</f>
         <v/>
       </c>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4">
-        <f>IF(M29="","",D29*M29)</f>
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -2300,11 +2077,6 @@
       </c>
       <c r="L30" s="9">
         <f>IF(J30="","",D30*J30)</f>
-        <v/>
-      </c>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="9">
-        <f>IF(M30="","",D30*M30)</f>
         <v/>
       </c>
     </row>
@@ -2349,11 +2121,6 @@
         <f>SUM(L3:L30)</f>
         <v/>
       </c>
-      <c r="M31" s="5" t="inlineStr"/>
-      <c r="N31" s="6">
-        <f>SUM(N3:N30)</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2365,19 +2132,6 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32">
         <f>SUMIF(J3:J30,"",D3:D30)</f>
-        <v/>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32">
-        <f>SUMIF(M3:M30,"",D3:D30)</f>
         <v/>
       </c>
     </row>
@@ -2392,7 +2146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2405,10 +2159,8 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2479,16 +2231,6 @@
           <t>Cost - new pigs (USD)</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Rate - unrated pigs at Pin (USD)</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2527,20 +2269,13 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L3" s="4">
         <f>IF(J3="","",D3*J3)</f>
         <v/>
       </c>
-      <c r="M3" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="N3" s="4">
-        <f>IF(M3="","",D3*M3)</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -2586,13 +2321,6 @@
         <f>IF(J4="","",D4*J4)</f>
         <v/>
       </c>
-      <c r="M4" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="N4" s="9">
-        <f>IF(M4="","",D4*M4)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2638,13 +2366,6 @@
         <f>IF(J5="","",D5*J5)</f>
         <v/>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N5" s="4">
-        <f>IF(M5="","",D5*M5)</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -2678,23 +2399,18 @@
       <c r="I6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="9" t="n"/>
+      <c r="J6" s="9" t="n">
+        <v>129.8</v>
+      </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L6" s="9">
         <f>IF(J6="","",D6*J6)</f>
         <v/>
       </c>
-      <c r="M6" s="9" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N6" s="9">
-        <f>IF(M6="","",D6*M6)</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2738,11 +2454,6 @@
         <f>IF(J7="","",D7*J7)</f>
         <v/>
       </c>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4">
-        <f>IF(M7="","",D7*M7)</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -2776,23 +2487,18 @@
       <c r="I8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="9" t="n"/>
+      <c r="J8" s="9" t="n">
+        <v>129.8</v>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L8" s="9">
         <f>IF(J8="","",D8*J8)</f>
         <v/>
       </c>
-      <c r="M8" s="9" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N8" s="9">
-        <f>IF(M8="","",D8*M8)</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2838,13 +2544,6 @@
         <f>IF(J9="","",D9*J9)</f>
         <v/>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N9" s="4">
-        <f>IF(M9="","",D9*M9)</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -2881,18 +2580,13 @@
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>no rate (size not on pigs.xlsx)</t>
         </is>
       </c>
       <c r="L10" s="9">
         <f>IF(J10="","",D10*J10)</f>
         <v/>
       </c>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="9">
-        <f>IF(M10="","",D10*M10)</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2934,11 +2628,6 @@
       </c>
       <c r="L11" s="4">
         <f>IF(J11="","",D11*J11)</f>
-        <v/>
-      </c>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4">
-        <f>IF(M11="","",D11*M11)</f>
         <v/>
       </c>
     </row>
@@ -2983,11 +2672,6 @@
         <f>SUM(L3:L11)</f>
         <v/>
       </c>
-      <c r="M12" s="5" t="inlineStr"/>
-      <c r="N12" s="6">
-        <f>SUM(N3:N11)</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2999,19 +2683,6 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13">
         <f>SUMIF(J3:J11,"",D3:D11)</f>
-        <v/>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13">
-        <f>SUMIF(M3:M11,"",D3:D11)</f>
         <v/>
       </c>
     </row>
@@ -3026,7 +2697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3039,10 +2710,8 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3113,16 +2782,6 @@
           <t>Cost - new pigs (USD)</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Rate - unrated pigs at Pin (USD)</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3166,11 +2825,6 @@
         <f>IF(J3="","",D3*J3)</f>
         <v/>
       </c>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4">
-        <f>IF(M3="","",D3*M3)</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -3214,11 +2868,6 @@
         <f>IF(J4="","",D4*J4)</f>
         <v/>
       </c>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="9">
-        <f>IF(M4="","",D4*M4)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3262,11 +2911,6 @@
         <f>IF(J5="","",D5*J5)</f>
         <v/>
       </c>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4">
-        <f>IF(M5="","",D5*M5)</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -3310,11 +2954,6 @@
         <f>IF(J6="","",D6*J6)</f>
         <v/>
       </c>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="9">
-        <f>IF(M6="","",D6*M6)</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3358,11 +2997,6 @@
         <f>IF(J7="","",D7*J7)</f>
         <v/>
       </c>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4">
-        <f>IF(M7="","",D7*M7)</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -3396,23 +3030,18 @@
       <c r="I8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="9" t="n"/>
+      <c r="J8" s="9" t="n">
+        <v>41.3</v>
+      </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L8" s="9">
         <f>IF(J8="","",D8*J8)</f>
         <v/>
       </c>
-      <c r="M8" s="9" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="N8" s="9">
-        <f>IF(M8="","",D8*M8)</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3458,13 +3087,6 @@
         <f>IF(J9="","",D9*J9)</f>
         <v/>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="N9" s="4">
-        <f>IF(M9="","",D9*M9)</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -3503,20 +3125,13 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L10" s="9">
         <f>IF(J10="","",D10*J10)</f>
         <v/>
       </c>
-      <c r="M10" s="9" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="N10" s="9">
-        <f>IF(M10="","",D10*M10)</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3555,20 +3170,13 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L11" s="4">
         <f>IF(J11="","",D11*J11)</f>
         <v/>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="N11" s="4">
-        <f>IF(M11="","",D11*M11)</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -3602,23 +3210,18 @@
       <c r="I12" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="9" t="n"/>
+      <c r="J12" s="9" t="n">
+        <v>41.3</v>
+      </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L12" s="9">
         <f>IF(J12="","",D12*J12)</f>
         <v/>
       </c>
-      <c r="M12" s="9" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="N12" s="9">
-        <f>IF(M12="","",D12*M12)</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3664,13 +3267,6 @@
         <f>IF(J13="","",D13*J13)</f>
         <v/>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="N13" s="4">
-        <f>IF(M13="","",D13*M13)</f>
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -3714,11 +3310,6 @@
         <f>IF(J14="","",D14*J14)</f>
         <v/>
       </c>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="9">
-        <f>IF(M14="","",D14*M14)</f>
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3762,11 +3353,6 @@
         <f>IF(J15="","",D15*J15)</f>
         <v/>
       </c>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4">
-        <f>IF(M15="","",D15*M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -3810,11 +3396,6 @@
         <f>IF(J16="","",D16*J16)</f>
         <v/>
       </c>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9">
-        <f>IF(M16="","",D16*M16)</f>
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3853,20 +3434,13 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L17" s="4">
         <f>IF(J17="","",D17*J17)</f>
         <v/>
       </c>
-      <c r="M17" s="4" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N17" s="4">
-        <f>IF(M17="","",D17*M17)</f>
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -3905,20 +3479,13 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L18" s="9">
         <f>IF(J18="","",D18*J18)</f>
         <v/>
       </c>
-      <c r="M18" s="9" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N18" s="9">
-        <f>IF(M18="","",D18*M18)</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3952,23 +3519,18 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="n"/>
+      <c r="J19" s="4" t="n">
+        <v>47.2</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L19" s="4">
         <f>IF(J19="","",D19*J19)</f>
         <v/>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N19" s="4">
-        <f>IF(M19="","",D19*M19)</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -4014,13 +3576,6 @@
         <f>IF(J20="","",D20*J20)</f>
         <v/>
       </c>
-      <c r="M20" s="9" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N20" s="9">
-        <f>IF(M20="","",D20*M20)</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4064,11 +3619,6 @@
         <f>IF(J21="","",D21*J21)</f>
         <v/>
       </c>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4">
-        <f>IF(M21="","",D21*M21)</f>
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -4112,11 +3662,6 @@
         <f>IF(J22="","",D22*J22)</f>
         <v/>
       </c>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9">
-        <f>IF(M22="","",D22*M22)</f>
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4153,18 +3698,13 @@
       <c r="J23" s="4" t="n"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>no rate (size not on pigs.xlsx)</t>
         </is>
       </c>
       <c r="L23" s="4">
         <f>IF(J23="","",D23*J23)</f>
         <v/>
       </c>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4">
-        <f>IF(M23="","",D23*M23)</f>
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -4208,11 +3748,6 @@
         <f>IF(J24="","",D24*J24)</f>
         <v/>
       </c>
-      <c r="M24" s="9" t="n"/>
-      <c r="N24" s="9">
-        <f>IF(M24="","",D24*M24)</f>
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4251,20 +3786,13 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L25" s="4">
         <f>IF(J25="","",D25*J25)</f>
         <v/>
       </c>
-      <c r="M25" s="4" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N25" s="4">
-        <f>IF(M25="","",D25*M25)</f>
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -4303,20 +3831,13 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L26" s="9">
         <f>IF(J26="","",D26*J26)</f>
         <v/>
       </c>
-      <c r="M26" s="9" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N26" s="9">
-        <f>IF(M26="","",D26*M26)</f>
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4350,23 +3871,18 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="n"/>
+      <c r="J27" s="4" t="n">
+        <v>47.2</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L27" s="4">
         <f>IF(J27="","",D27*J27)</f>
         <v/>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N27" s="4">
-        <f>IF(M27="","",D27*M27)</f>
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -4412,13 +3928,6 @@
         <f>IF(J28="","",D28*J28)</f>
         <v/>
       </c>
-      <c r="M28" s="9" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="N28" s="9">
-        <f>IF(M28="","",D28*M28)</f>
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4462,11 +3971,6 @@
         <f>IF(J29="","",D29*J29)</f>
         <v/>
       </c>
-      <c r="M29" s="4" t="n"/>
-      <c r="N29" s="4">
-        <f>IF(M29="","",D29*M29)</f>
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -4505,20 +4009,13 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L30" s="9">
         <f>IF(J30="","",D30*J30)</f>
         <v/>
       </c>
-      <c r="M30" s="9" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="N30" s="9">
-        <f>IF(M30="","",D30*M30)</f>
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4562,11 +4059,6 @@
         <f>IF(J31="","",D31*J31)</f>
         <v/>
       </c>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4">
-        <f>IF(M31="","",D31*M31)</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -4610,11 +4102,6 @@
         <f>IF(J32="","",D32*J32)</f>
         <v/>
       </c>
-      <c r="M32" s="9" t="n"/>
-      <c r="N32" s="9">
-        <f>IF(M32="","",D32*M32)</f>
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4653,20 +4140,13 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L33" s="4">
         <f>IF(J33="","",D33*J33)</f>
         <v/>
       </c>
-      <c r="M33" s="4" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="N33" s="4">
-        <f>IF(M33="","",D33*M33)</f>
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -4700,23 +4180,18 @@
       <c r="I34" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="9" t="n"/>
+      <c r="J34" s="9" t="n">
+        <v>53.1</v>
+      </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L34" s="9">
         <f>IF(J34="","",D34*J34)</f>
         <v/>
       </c>
-      <c r="M34" s="9" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="N34" s="9">
-        <f>IF(M34="","",D34*M34)</f>
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4762,13 +4237,6 @@
         <f>IF(J35="","",D35*J35)</f>
         <v/>
       </c>
-      <c r="M35" s="4" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="N35" s="4">
-        <f>IF(M35="","",D35*M35)</f>
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -4812,11 +4280,6 @@
         <f>IF(J36="","",D36*J36)</f>
         <v/>
       </c>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="9">
-        <f>IF(M36="","",D36*M36)</f>
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4860,11 +4323,6 @@
         <f>IF(J37="","",D37*J37)</f>
         <v/>
       </c>
-      <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4">
-        <f>IF(M37="","",D37*M37)</f>
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -4908,11 +4366,6 @@
         <f>IF(J38="","",D38*J38)</f>
         <v/>
       </c>
-      <c r="M38" s="9" t="n"/>
-      <c r="N38" s="9">
-        <f>IF(M38="","",D38*M38)</f>
-        <v/>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4951,20 +4404,13 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L39" s="4">
         <f>IF(J39="","",D39*J39)</f>
         <v/>
       </c>
-      <c r="M39" s="4" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="N39" s="4">
-        <f>IF(M39="","",D39*M39)</f>
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -5008,11 +4454,6 @@
         <f>IF(J40="","",D40*J40)</f>
         <v/>
       </c>
-      <c r="M40" s="9" t="n"/>
-      <c r="N40" s="9">
-        <f>IF(M40="","",D40*M40)</f>
-        <v/>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5058,13 +4499,6 @@
         <f>IF(J41="","",D41*J41)</f>
         <v/>
       </c>
-      <c r="M41" s="4" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="N41" s="4">
-        <f>IF(M41="","",D41*M41)</f>
-        <v/>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -5108,11 +4542,6 @@
         <f>IF(J42="","",D42*J42)</f>
         <v/>
       </c>
-      <c r="M42" s="9" t="n"/>
-      <c r="N42" s="9">
-        <f>IF(M42="","",D42*M42)</f>
-        <v/>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5151,20 +4580,13 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L43" s="4">
         <f>IF(J43="","",D43*J43)</f>
         <v/>
       </c>
-      <c r="M43" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="N43" s="4">
-        <f>IF(M43="","",D43*M43)</f>
-        <v/>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -5210,13 +4632,6 @@
         <f>IF(J44="","",D44*J44)</f>
         <v/>
       </c>
-      <c r="M44" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N44" s="9">
-        <f>IF(M44="","",D44*M44)</f>
-        <v/>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5262,13 +4677,6 @@
         <f>IF(J45="","",D45*J45)</f>
         <v/>
       </c>
-      <c r="M45" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="N45" s="4">
-        <f>IF(M45="","",D45*M45)</f>
-        <v/>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -5312,11 +4720,6 @@
         <f>IF(J46="","",D46*J46)</f>
         <v/>
       </c>
-      <c r="M46" s="9" t="n"/>
-      <c r="N46" s="9">
-        <f>IF(M46="","",D46*M46)</f>
-        <v/>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5358,11 +4761,6 @@
       </c>
       <c r="L47" s="4">
         <f>IF(J47="","",D47*J47)</f>
-        <v/>
-      </c>
-      <c r="M47" s="4" t="n"/>
-      <c r="N47" s="4">
-        <f>IF(M47="","",D47*M47)</f>
         <v/>
       </c>
     </row>
@@ -5407,11 +4805,6 @@
         <f>SUM(L3:L47)</f>
         <v/>
       </c>
-      <c r="M48" s="5" t="inlineStr"/>
-      <c r="N48" s="6">
-        <f>SUM(N3:N47)</f>
-        <v/>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5423,19 +4816,6 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49">
         <f>SUMIF(J3:J47,"",D3:D47)</f>
-        <v/>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49">
-        <f>SUMIF(M3:M47,"",D3:D47)</f>
         <v/>
       </c>
     </row>
@@ -5450,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5463,10 +4843,8 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5537,16 +4915,6 @@
           <t>Cost - new pigs (USD)</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>Rate - unrated pigs at Pin (USD)</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>Cost - new pigs, unrated at Pin rate (USD)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5585,20 +4953,13 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L3" s="4">
         <f>IF(J3="","",D3*J3)</f>
         <v/>
       </c>
-      <c r="M3" s="4" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="N3" s="4">
-        <f>IF(M3="","",D3*M3)</f>
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -5644,13 +5005,6 @@
         <f>IF(J4="","",D4*J4)</f>
         <v/>
       </c>
-      <c r="M4" s="9" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="N4" s="9">
-        <f>IF(M4="","",D4*M4)</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5694,11 +5048,6 @@
         <f>IF(J5="","",D5*J5)</f>
         <v/>
       </c>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4">
-        <f>IF(M5="","",D5*M5)</f>
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -5744,13 +5093,6 @@
         <f>IF(J6="","",D6*J6)</f>
         <v/>
       </c>
-      <c r="M6" s="9" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="N6" s="9">
-        <f>IF(M6="","",D6*M6)</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5796,13 +5138,6 @@
         <f>IF(J7="","",D7*J7)</f>
         <v/>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N7" s="4">
-        <f>IF(M7="","",D7*M7)</f>
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -5848,13 +5183,6 @@
         <f>IF(J8="","",D8*J8)</f>
         <v/>
       </c>
-      <c r="M8" s="9" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N8" s="9">
-        <f>IF(M8="","",D8*M8)</f>
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5893,20 +5221,13 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L9" s="4">
         <f>IF(J9="","",D9*J9)</f>
         <v/>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="N9" s="4">
-        <f>IF(M9="","",D9*M9)</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -5952,13 +5273,6 @@
         <f>IF(J10="","",D10*J10)</f>
         <v/>
       </c>
-      <c r="M10" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="N10" s="9">
-        <f>IF(M10="","",D10*M10)</f>
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6002,11 +5316,6 @@
         <f>IF(J11="","",D11*J11)</f>
         <v/>
       </c>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4">
-        <f>IF(M11="","",D11*M11)</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -6052,13 +5361,6 @@
         <f>IF(J12="","",D12*J12)</f>
         <v/>
       </c>
-      <c r="M12" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="N12" s="9">
-        <f>IF(M12="","",D12*M12)</f>
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6104,13 +5406,6 @@
         <f>IF(J13="","",D13*J13)</f>
         <v/>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="N13" s="4">
-        <f>IF(M13="","",D13*M13)</f>
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -6149,20 +5444,13 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L14" s="9">
         <f>IF(J14="","",D14*J14)</f>
         <v/>
       </c>
-      <c r="M14" s="9" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="N14" s="9">
-        <f>IF(M14="","",D14*M14)</f>
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6208,13 +5496,6 @@
         <f>IF(J15="","",D15*J15)</f>
         <v/>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="N15" s="4">
-        <f>IF(M15="","",D15*M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -6258,11 +5539,6 @@
         <f>IF(J16="","",D16*J16)</f>
         <v/>
       </c>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9">
-        <f>IF(M16="","",D16*M16)</f>
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6306,11 +5582,6 @@
         <f>IF(J17="","",D17*J17)</f>
         <v/>
       </c>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4">
-        <f>IF(M17="","",D17*M17)</f>
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -6354,11 +5625,6 @@
         <f>IF(J18="","",D18*J18)</f>
         <v/>
       </c>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="9">
-        <f>IF(M18="","",D18*M18)</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6404,13 +5670,6 @@
         <f>IF(J19="","",D19*J19)</f>
         <v/>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="N19" s="4">
-        <f>IF(M19="","",D19*M19)</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -6456,13 +5715,6 @@
         <f>IF(J20="","",D20*J20)</f>
         <v/>
       </c>
-      <c r="M20" s="9" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="N20" s="9">
-        <f>IF(M20="","",D20*M20)</f>
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6496,23 +5748,18 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="4" t="n"/>
+      <c r="J21" s="4" t="n">
+        <v>118</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L21" s="4">
         <f>IF(J21="","",D21*J21)</f>
         <v/>
       </c>
-      <c r="M21" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="N21" s="4">
-        <f>IF(M21="","",D21*M21)</f>
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -6558,13 +5805,6 @@
         <f>IF(J22="","",D22*J22)</f>
         <v/>
       </c>
-      <c r="M22" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="N22" s="9">
-        <f>IF(M22="","",D22*M22)</f>
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6610,13 +5850,6 @@
         <f>IF(J23="","",D23*J23)</f>
         <v/>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N23" s="4">
-        <f>IF(M23="","",D23*M23)</f>
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -6660,11 +5893,6 @@
         <f>IF(J24="","",D24*J24)</f>
         <v/>
       </c>
-      <c r="M24" s="9" t="n"/>
-      <c r="N24" s="9">
-        <f>IF(M24="","",D24*M24)</f>
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6710,13 +5938,6 @@
         <f>IF(J25="","",D25*J25)</f>
         <v/>
       </c>
-      <c r="M25" s="4" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="N25" s="4">
-        <f>IF(M25="","",D25*M25)</f>
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -6755,20 +5976,13 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L26" s="9">
         <f>IF(J26="","",D26*J26)</f>
         <v/>
       </c>
-      <c r="M26" s="9" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="N26" s="9">
-        <f>IF(M26="","",D26*M26)</f>
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6812,11 +6026,6 @@
         <f>IF(J27="","",D27*J27)</f>
         <v/>
       </c>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4">
-        <f>IF(M27="","",D27*M27)</f>
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -6862,13 +6071,6 @@
         <f>IF(J28="","",D28*J28)</f>
         <v/>
       </c>
-      <c r="M28" s="9" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="N28" s="9">
-        <f>IF(M28="","",D28*M28)</f>
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6914,13 +6116,6 @@
         <f>IF(J29="","",D29*J29)</f>
         <v/>
       </c>
-      <c r="M29" s="4" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="N29" s="4">
-        <f>IF(M29="","",D29*M29)</f>
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -6959,20 +6154,13 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L30" s="9">
         <f>IF(J30="","",D30*J30)</f>
         <v/>
       </c>
-      <c r="M30" s="9" t="n">
-        <v>483.8</v>
-      </c>
-      <c r="N30" s="9">
-        <f>IF(M30="","",D30*M30)</f>
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7018,13 +6206,6 @@
         <f>IF(J31="","",D31*J31)</f>
         <v/>
       </c>
-      <c r="M31" s="4" t="n">
-        <v>483.8</v>
-      </c>
-      <c r="N31" s="4">
-        <f>IF(M31="","",D31*M31)</f>
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -7070,13 +6251,6 @@
         <f>IF(J32="","",D32*J32)</f>
         <v/>
       </c>
-      <c r="M32" s="9" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="N32" s="9">
-        <f>IF(M32="","",D32*M32)</f>
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7120,11 +6294,6 @@
         <f>IF(J33="","",D33*J33)</f>
         <v/>
       </c>
-      <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4">
-        <f>IF(M33="","",D33*M33)</f>
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -7163,20 +6332,13 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx Pin rate, same size</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L34" s="9">
         <f>IF(J34="","",D34*J34)</f>
         <v/>
       </c>
-      <c r="M34" s="9" t="n">
-        <v>826</v>
-      </c>
-      <c r="N34" s="9">
-        <f>IF(M34="","",D34*M34)</f>
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7222,13 +6384,6 @@
         <f>IF(J35="","",D35*J35)</f>
         <v/>
       </c>
-      <c r="M35" s="4" t="n">
-        <v>826</v>
-      </c>
-      <c r="N35" s="4">
-        <f>IF(M35="","",D35*M35)</f>
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -7272,11 +6427,6 @@
         <f>IF(J36="","",D36*J36)</f>
         <v/>
       </c>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="9">
-        <f>IF(M36="","",D36*M36)</f>
-        <v/>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7320,11 +6470,6 @@
         <f>IF(J37="","",D37*J37)</f>
         <v/>
       </c>
-      <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4">
-        <f>IF(M37="","",D37*M37)</f>
-        <v/>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -7366,11 +6511,6 @@
       </c>
       <c r="L38" s="9">
         <f>IF(J38="","",D38*J38)</f>
-        <v/>
-      </c>
-      <c r="M38" s="9" t="n"/>
-      <c r="N38" s="9">
-        <f>IF(M38="","",D38*M38)</f>
         <v/>
       </c>
     </row>
@@ -7415,11 +6555,6 @@
         <f>SUM(L3:L38)</f>
         <v/>
       </c>
-      <c r="M39" s="5" t="inlineStr"/>
-      <c r="N39" s="6">
-        <f>SUM(N3:N38)</f>
-        <v/>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7431,19 +6566,6 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40">
         <f>SUMIF(J3:J38,"",D3:D38)</f>
-        <v/>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40">
-        <f>SUMIF(M3:M38,"",D3:D38)</f>
         <v/>
       </c>
     </row>

--- a/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
+++ b/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
@@ -733,7 +733,7 @@
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Costing: New pigs only; used pigs are not costed (Jesse, 2026-10-02). Rates are from pigs.xlsx for the same size and type. Any pig without its own rate is priced as Pin at the same size (Jesse, 2026-10-02: "Unrated are priced as PIN"). Foam takes the Gauge Foam rate; foams, swabs and honeycomb are not repriced as Pin. Sizes not on pigs.xlsx at all carry no rate and are counted in "New pigs with no rate".</t>
+          <t>Costing: New pigs only; used pigs are not costed (Jesse, 2026-10-02). Rates are from pigs.xlsx for the same size and type. Any pig without its own rate is priced as Pin (Jesse, 2026-10-02: "Unrated are priced as PIN"); foams use the Gauge Foam list and swabs the Swab list. A size not on the list rounds UP to the next listed size (Jesse, 2026-10-02). Only illegible sizes and sizes above the largest listed one stay unpriced.</t>
         </is>
       </c>
     </row>
@@ -870,10 +870,12 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="n"/>
+      <c r="J3" s="4" t="n">
+        <v>118</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 6" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L3" s="4">
@@ -913,10 +915,12 @@
       <c r="I4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="9" t="n"/>
+      <c r="J4" s="9" t="n">
+        <v>118</v>
+      </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 6" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L4" s="9">
@@ -1406,10 +1410,12 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="n"/>
+      <c r="J15" s="4" t="n">
+        <v>182.9</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 7.25" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L15" s="4">
@@ -1449,10 +1455,12 @@
       <c r="I16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="9" t="n"/>
+      <c r="J16" s="9" t="n">
+        <v>230.1</v>
+      </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 8" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L16" s="9">
@@ -1492,10 +1500,12 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="n"/>
+      <c r="J17" s="4" t="n">
+        <v>230.1</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 8" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L17" s="4">
@@ -1535,10 +1545,12 @@
       <c r="I18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="9" t="n"/>
+      <c r="J18" s="9" t="n">
+        <v>230.1</v>
+      </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 8" Pin</t>
         </is>
       </c>
       <c r="L18" s="9">
@@ -1851,7 +1863,7 @@
       <c r="J25" s="4" t="n"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>no rate (above the largest listed gauge foam)</t>
         </is>
       </c>
       <c r="L25" s="4">
@@ -2029,7 +2041,7 @@
       <c r="J29" s="4" t="n"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>no rate (above the largest listed swab)</t>
         </is>
       </c>
       <c r="L29" s="4">
@@ -2444,10 +2456,12 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="n"/>
+      <c r="J7" s="4" t="n">
+        <v>82.59999999999999</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 8" Gauge Foam</t>
         </is>
       </c>
       <c r="L7" s="4">
@@ -2577,10 +2591,12 @@
       <c r="I10" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="9" t="n"/>
+      <c r="J10" s="9" t="n">
+        <v>182.9</v>
+      </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 7.25" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L10" s="9">
@@ -2815,10 +2831,12 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="n"/>
+      <c r="J3" s="4" t="n">
+        <v>35.4</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.125" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L3" s="4">
@@ -2858,10 +2876,12 @@
       <c r="I4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="9" t="n"/>
+      <c r="J4" s="9" t="n">
+        <v>35.4</v>
+      </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.125" Pin</t>
         </is>
       </c>
       <c r="L4" s="9">
@@ -2901,10 +2921,12 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="n"/>
+      <c r="J5" s="4" t="n">
+        <v>35.4</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.125" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L5" s="4">
@@ -2944,10 +2966,12 @@
       <c r="I6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="9" t="n"/>
+      <c r="J6" s="9" t="n">
+        <v>35.4</v>
+      </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.125" Pin</t>
         </is>
       </c>
       <c r="L6" s="9">
@@ -2987,10 +3011,12 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="n"/>
+      <c r="J7" s="4" t="n">
+        <v>16.5</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.625" Gauge Foam</t>
         </is>
       </c>
       <c r="L7" s="4">
@@ -3300,10 +3326,12 @@
       <c r="I14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="9" t="n"/>
+      <c r="J14" s="9" t="n">
+        <v>41.3</v>
+      </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>no rate (type not on pigs.xlsx)</t>
+          <t>rounded up to 3.325" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L14" s="9">
@@ -3343,10 +3371,12 @@
       <c r="I15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="4" t="n"/>
+      <c r="J15" s="4" t="n">
+        <v>47.2</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.5" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L15" s="4">
@@ -3386,10 +3416,12 @@
       <c r="I16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="9" t="n"/>
+      <c r="J16" s="9" t="n">
+        <v>47.2</v>
+      </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.5" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L16" s="9">
@@ -3609,10 +3641,12 @@
       <c r="I21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="4" t="n"/>
+      <c r="J21" s="4" t="n">
+        <v>47.2</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.625" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L21" s="4">
@@ -3652,10 +3686,12 @@
       <c r="I22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="9" t="n"/>
+      <c r="J22" s="9" t="n">
+        <v>47.2</v>
+      </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.625" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L22" s="9">
@@ -3695,10 +3731,12 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="n"/>
+      <c r="J23" s="4" t="n">
+        <v>47.2</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.625" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L23" s="4">
@@ -3738,10 +3776,12 @@
       <c r="I24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="9" t="n"/>
+      <c r="J24" s="9" t="n">
+        <v>47.2</v>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.625" Pin</t>
         </is>
       </c>
       <c r="L24" s="9">
@@ -3961,10 +4001,12 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="n"/>
+      <c r="J29" s="4" t="n">
+        <v>53.1</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.75" Pin</t>
         </is>
       </c>
       <c r="L29" s="4">
@@ -4049,10 +4091,12 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="n"/>
+      <c r="J31" s="4" t="n">
+        <v>18.9</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 4" Gauge Foam</t>
         </is>
       </c>
       <c r="L31" s="4">
@@ -4092,10 +4136,12 @@
       <c r="I32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="9" t="n"/>
+      <c r="J32" s="9" t="n">
+        <v>18.9</v>
+      </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 4" Gauge Foam</t>
         </is>
       </c>
       <c r="L32" s="9">
@@ -4270,10 +4316,12 @@
       <c r="I36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="9" t="n"/>
+      <c r="J36" s="9" t="n">
+        <v>18.9</v>
+      </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 4" Gauge Foam</t>
         </is>
       </c>
       <c r="L36" s="9">
@@ -4313,10 +4361,12 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="4" t="n"/>
+      <c r="J37" s="4" t="n">
+        <v>53.1</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.875" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L37" s="4">
@@ -4356,10 +4406,12 @@
       <c r="I38" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J38" s="9" t="n"/>
+      <c r="J38" s="9" t="n">
+        <v>53.1</v>
+      </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.875" Pin</t>
         </is>
       </c>
       <c r="L38" s="9">
@@ -4444,10 +4496,12 @@
       <c r="I40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="9" t="n"/>
+      <c r="J40" s="9" t="n">
+        <v>18.9</v>
+      </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 4" Gauge Foam</t>
         </is>
       </c>
       <c r="L40" s="9">
@@ -4532,10 +4586,12 @@
       <c r="I42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="9" t="n"/>
+      <c r="J42" s="9" t="n">
+        <v>59</v>
+      </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 4" Pin</t>
         </is>
       </c>
       <c r="L42" s="9">
@@ -4710,10 +4766,12 @@
       <c r="I46" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="9" t="n"/>
+      <c r="J46" s="9" t="n">
+        <v>16.1</v>
+      </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 8.5" Swab</t>
         </is>
       </c>
       <c r="L46" s="9">
@@ -5038,10 +5096,12 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="n"/>
+      <c r="J5" s="4" t="n">
+        <v>53.1</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 3.875" Pin</t>
         </is>
       </c>
       <c r="L5" s="4">
@@ -5306,10 +5366,12 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="n"/>
+      <c r="J11" s="4" t="n">
+        <v>59</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 4.125" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L11" s="4">
@@ -5529,10 +5591,12 @@
       <c r="I16" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="9" t="n"/>
+      <c r="J16" s="9" t="n">
+        <v>118</v>
+      </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 6" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L16" s="9">
@@ -5572,10 +5636,12 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="n"/>
+      <c r="J17" s="4" t="n">
+        <v>118</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 6" Pin</t>
         </is>
       </c>
       <c r="L17" s="4">
@@ -5615,10 +5681,12 @@
       <c r="I18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="9" t="n"/>
+      <c r="J18" s="9" t="n">
+        <v>118</v>
+      </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 6" Pin</t>
         </is>
       </c>
       <c r="L18" s="9">
@@ -5883,10 +5951,12 @@
       <c r="I24" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="9" t="n"/>
+      <c r="J24" s="9" t="n">
+        <v>82.59999999999999</v>
+      </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 8" Gauge Foam</t>
         </is>
       </c>
       <c r="L24" s="9">
@@ -6016,10 +6086,12 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="4" t="n"/>
+      <c r="J27" s="4" t="n">
+        <v>16.1</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 8.5" Swab</t>
         </is>
       </c>
       <c r="L27" s="4">
@@ -6284,10 +6356,12 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="4" t="n"/>
+      <c r="J33" s="4" t="n">
+        <v>826</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>rounded up to 12" Pin</t>
         </is>
       </c>
       <c r="L33" s="4">
@@ -6420,7 +6494,7 @@
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>no rate (size not on pigs.xlsx)</t>
+          <t>no rate (above the largest listed pin)</t>
         </is>
       </c>
       <c r="L36" s="9">

--- a/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
+++ b/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
@@ -1860,10 +1860,12 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="4" t="n"/>
+      <c r="J25" s="4" t="n">
+        <v>82.59999999999999</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>no rate (above the largest listed gauge foam)</t>
+          <t>above the list - charged as 8" Gauge Foam</t>
         </is>
       </c>
       <c r="L25" s="4">
@@ -2038,10 +2040,12 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="n"/>
+      <c r="J29" s="4" t="n">
+        <v>26.5</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>no rate (above the largest listed swab)</t>
+          <t>above the list - charged as 10" Swab</t>
         </is>
       </c>
       <c r="L29" s="4">
@@ -6491,10 +6495,12 @@
       <c r="I36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="9" t="n"/>
+      <c r="J36" s="9" t="n">
+        <v>826</v>
+      </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>no rate (above the largest listed pin)</t>
+          <t>above the list - charged as 12" Pin</t>
         </is>
       </c>
       <c r="L36" s="9">

--- a/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
+++ b/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
@@ -571,11 +571,11 @@
         <v>25</v>
       </c>
       <c r="I5" s="4">
-        <f>'Crude'!L31</f>
+        <f>'Crude'!L30</f>
         <v/>
       </c>
       <c r="J5">
-        <f>'Crude'!D32</f>
+        <f>'Crude'!D31</f>
         <v/>
       </c>
     </row>
@@ -643,11 +643,11 @@
         <v>25</v>
       </c>
       <c r="I7" s="4">
-        <f>'Coker'!L48</f>
+        <f>'Coker'!L47</f>
         <v/>
       </c>
       <c r="J7">
-        <f>'Coker'!D49</f>
+        <f>'Coker'!D48</f>
         <v/>
       </c>
     </row>
@@ -679,11 +679,11 @@
         <v>5</v>
       </c>
       <c r="I8" s="4">
-        <f>'Vac'!L39</f>
+        <f>'Vac'!L38</f>
         <v/>
       </c>
       <c r="J8">
-        <f>'Vac'!D40</f>
+        <f>'Vac'!D39</f>
         <v/>
       </c>
     </row>
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>4</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>1</v>
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>1</v>
@@ -2054,100 +2054,57 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>size not legible</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Foam</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>no rate (size not legible)</t>
-        </is>
-      </c>
-      <c r="L30" s="9">
-        <f>IF(J30="","",D30*J30)</f>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5">
+        <f>SUM(C3:C29)</f>
         <v/>
       </c>
+      <c r="D30" s="5">
+        <f>SUM(D3:D29)</f>
+        <v/>
+      </c>
+      <c r="E30" s="5">
+        <f>SUM(E3:E29)</f>
+        <v/>
+      </c>
+      <c r="F30" s="5">
+        <f>SUM(F3:F29)</f>
+        <v/>
+      </c>
+      <c r="G30" s="5">
+        <f>SUM(G3:G29)</f>
+        <v/>
+      </c>
+      <c r="H30" s="5">
+        <f>SUM(H3:H29)</f>
+        <v/>
+      </c>
+      <c r="I30" s="5">
+        <f>SUM(I3:I29)</f>
+        <v/>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="6">
+        <f>SUM(L3:L29)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr"/>
-      <c r="C31" s="5">
-        <f>SUM(C3:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="5">
-        <f>SUM(D3:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="5">
-        <f>SUM(E3:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="5">
-        <f>SUM(F3:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="5">
-        <f>SUM(G3:G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="5">
-        <f>SUM(H3:H30)</f>
-        <v/>
-      </c>
-      <c r="I31" s="5">
-        <f>SUM(I3:I30)</f>
-        <v/>
-      </c>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr"/>
-      <c r="L31" s="6">
-        <f>SUM(L3:L30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>New pigs with no rate</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32">
-        <f>SUMIF(J3:J30,"",D3:D30)</f>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31">
+        <f>SUMIF(J3:J29,"",D3:D29)</f>
         <v/>
       </c>
     </row>
@@ -2256,36 +2213,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>118</v>
+        <v>49.6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>priced as Pin, same size</t>
+          <t>pigs.xlsx (Gauge Foam rate)</t>
         </is>
       </c>
       <c r="L3" s="4">
@@ -2301,26 +2258,26 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Pin / TC / PPS</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C4" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="H4" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="8" t="n">
         <v>0</v>
@@ -2330,7 +2287,7 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>pigs.xlsx</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L4" s="9">
@@ -2341,37 +2298,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6.25"</t>
+          <t>6"</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bolted</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>129.8</v>
+        <v>118</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -2391,36 +2348,36 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>FMJ</t>
+          <t>Bolted</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="H6" s="8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>129.8</v>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>priced as Pin, same size</t>
+          <t>pigs.xlsx</t>
         </is>
       </c>
       <c r="L6" s="9">
@@ -2436,14 +2393,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>FMJ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2452,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2461,11 +2418,11 @@
         <v>0</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>82.59999999999999</v>
+        <v>129.8</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>rounded up to 8" Gauge Foam</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L7" s="4">
@@ -2481,14 +2438,14 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Other / unclear</t>
+          <t>Foam</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>0</v>
@@ -2497,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>0</v>
@@ -2506,11 +2463,11 @@
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>129.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>priced as Pin, same size</t>
+          <t>rounded up to 8" Gauge Foam</t>
         </is>
       </c>
       <c r="L8" s="9">
@@ -2526,26 +2483,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pin / TC / PPS</t>
+          <t>Other / unclear</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2555,7 +2512,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>pigs.xlsx</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L9" s="4">
@@ -2566,41 +2523,41 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>6.5"</t>
+          <t>6.25"</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Other / unclear</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>182.9</v>
+        <v>129.8</v>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>rounded up to 7.25" Pin (priced as Pin)</t>
+          <t>pigs.xlsx</t>
         </is>
       </c>
       <c r="L10" s="9">
@@ -2611,19 +2568,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>size not legible</t>
+          <t>6.5"</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Foam</t>
+          <t>Other / unclear</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2632,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -2640,10 +2597,12 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="n"/>
+      <c r="J11" s="4" t="n">
+        <v>182.9</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>no rate (size not legible)</t>
+          <t>rounded up to 7.25" Pin (priced as Pin)</t>
         </is>
       </c>
       <c r="L11" s="4">
@@ -2717,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4075,10 +4034,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -4087,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -4784,100 +4743,57 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>size not legible</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Foam</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>no rate (size not legible)</t>
-        </is>
-      </c>
-      <c r="L47" s="4">
-        <f>IF(J47="","",D47*J47)</f>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr"/>
+      <c r="C47" s="5">
+        <f>SUM(C3:C46)</f>
         <v/>
       </c>
+      <c r="D47" s="5">
+        <f>SUM(D3:D46)</f>
+        <v/>
+      </c>
+      <c r="E47" s="5">
+        <f>SUM(E3:E46)</f>
+        <v/>
+      </c>
+      <c r="F47" s="5">
+        <f>SUM(F3:F46)</f>
+        <v/>
+      </c>
+      <c r="G47" s="5">
+        <f>SUM(G3:G46)</f>
+        <v/>
+      </c>
+      <c r="H47" s="5">
+        <f>SUM(H3:H46)</f>
+        <v/>
+      </c>
+      <c r="I47" s="5">
+        <f>SUM(I3:I46)</f>
+        <v/>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr"/>
+      <c r="L47" s="6">
+        <f>SUM(L3:L46)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
-      <c r="C48" s="5">
-        <f>SUM(C3:C47)</f>
-        <v/>
-      </c>
-      <c r="D48" s="5">
-        <f>SUM(D3:D47)</f>
-        <v/>
-      </c>
-      <c r="E48" s="5">
-        <f>SUM(E3:E47)</f>
-        <v/>
-      </c>
-      <c r="F48" s="5">
-        <f>SUM(F3:F47)</f>
-        <v/>
-      </c>
-      <c r="G48" s="5">
-        <f>SUM(G3:G47)</f>
-        <v/>
-      </c>
-      <c r="H48" s="5">
-        <f>SUM(H3:H47)</f>
-        <v/>
-      </c>
-      <c r="I48" s="5">
-        <f>SUM(I3:I47)</f>
-        <v/>
-      </c>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr"/>
-      <c r="L48" s="6">
-        <f>SUM(L3:L47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>New pigs with no rate</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49">
-        <f>SUMIF(J3:J47,"",D3:D47)</f>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48">
+        <f>SUMIF(J3:J46,"",D3:D46)</f>
         <v/>
       </c>
     </row>
@@ -4892,7 +4808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5530,22 +5446,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -6196,41 +6112,41 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>10"</t>
+          <t>8.25"</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Swab</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I30" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>483.8</v>
+        <v>16.1</v>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>priced as Pin, same size</t>
+          <t>rounded up to 8.5" Swab</t>
         </is>
       </c>
       <c r="L30" s="9">
@@ -6246,26 +6162,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pin / TC / PPS</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
         <v>4</v>
       </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3</v>
-      </c>
       <c r="F31" t="n">
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -6275,7 +6191,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>pigs.xlsx</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L31" s="4">
@@ -6291,32 +6207,32 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Swab</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
         <v>4</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>4</v>
-      </c>
       <c r="H32" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>26.5</v>
+        <v>483.8</v>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
@@ -6331,41 +6247,41 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10.25"</t>
+          <t>10"</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pin / TC / PPS</t>
+          <t>Swab</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
         <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="n">
         <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>826</v>
+        <v>26.5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>rounded up to 12" Pin</t>
+          <t>pigs.xlsx</t>
         </is>
       </c>
       <c r="L33" s="4">
@@ -6376,31 +6292,31 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>12"</t>
+          <t>10.25"</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Pin / TC / PPS</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>0</v>
@@ -6410,7 +6326,7 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>priced as Pin, same size</t>
+          <t>rounded up to 12" Pin</t>
         </is>
       </c>
       <c r="L34" s="9">
@@ -6426,7 +6342,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pin / TC / PPS</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -6455,7 +6371,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>pigs.xlsx</t>
+          <t>priced as Pin, same size</t>
         </is>
       </c>
       <c r="L35" s="4">
@@ -6466,7 +6382,7 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>12.25"</t>
+          <t>12"</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -6475,13 +6391,13 @@
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D36" s="8" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>1</v>
@@ -6490,7 +6406,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I36" s="8" t="n">
         <v>0</v>
@@ -6500,7 +6416,7 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>above the list - charged as 12" Pin</t>
+          <t>pigs.xlsx</t>
         </is>
       </c>
       <c r="L36" s="9">
@@ -6511,7 +6427,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>size not legible</t>
+          <t>12.25"</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6520,13 +6436,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>1</v>
@@ -6535,15 +6451,17 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
-      <c r="J37" s="4" t="n"/>
+      <c r="J37" s="4" t="n">
+        <v>826</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>no rate (size not legible)</t>
+          <t>above the list - charged as 12" Pin</t>
         </is>
       </c>
       <c r="L37" s="4">
@@ -6552,100 +6470,57 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>size not legible</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Swab</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>no rate (size not legible)</t>
-        </is>
-      </c>
-      <c r="L38" s="9">
-        <f>IF(J38="","",D38*J38)</f>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="5">
+        <f>SUM(C3:C37)</f>
         <v/>
       </c>
+      <c r="D38" s="5">
+        <f>SUM(D3:D37)</f>
+        <v/>
+      </c>
+      <c r="E38" s="5">
+        <f>SUM(E3:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="5">
+        <f>SUM(F3:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="5">
+        <f>SUM(G3:G37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="5">
+        <f>SUM(H3:H37)</f>
+        <v/>
+      </c>
+      <c r="I38" s="5">
+        <f>SUM(I3:I37)</f>
+        <v/>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="6">
+        <f>SUM(L3:L37)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr"/>
-      <c r="C39" s="5">
-        <f>SUM(C3:C38)</f>
-        <v/>
-      </c>
-      <c r="D39" s="5">
-        <f>SUM(D3:D38)</f>
-        <v/>
-      </c>
-      <c r="E39" s="5">
-        <f>SUM(E3:E38)</f>
-        <v/>
-      </c>
-      <c r="F39" s="5">
-        <f>SUM(F3:F38)</f>
-        <v/>
-      </c>
-      <c r="G39" s="5">
-        <f>SUM(G3:G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="5">
-        <f>SUM(H3:H38)</f>
-        <v/>
-      </c>
-      <c r="I39" s="5">
-        <f>SUM(I3:I38)</f>
-        <v/>
-      </c>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr"/>
-      <c r="L39" s="6">
-        <f>SUM(L3:L38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>New pigs with no rate</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40">
-        <f>SUMIF(J3:J38,"",D3:D38)</f>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39">
+        <f>SUMIF(J3:J37,"",D3:D37)</f>
         <v/>
       </c>
     </row>
@@ -9564,7 +9439,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>size not legible</t>
+          <t>3.75"</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -9592,7 +9467,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>no size written; Push Foam col marked</t>
+          <t>no size written; Push Foam col marked; size 3.75" per Jesse 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -17387,7 +17262,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>size not legible</t>
+          <t>6"</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -17415,7 +17290,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>no size written; side: RIGHT struck through on header</t>
+          <t>no size written; side: RIGHT struck through on header; size 6" per Jesse 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -28038,7 +27913,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>size not legible</t>
+          <t>6"</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -28066,7 +27941,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>08:00; Push Foam ticked; size not written</t>
+          <t>08:00; Push Foam ticked; size not written; size 6" per Jesse 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -31652,7 +31527,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>size not legible</t>
+          <t>4.25"</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -31680,7 +31555,7 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>size digit hidden by folded page corner; time 6:00</t>
+          <t>size digit hidden by folded page corner; time 6:00; size 4.25" per Jesse 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -31705,7 +31580,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>size not legible</t>
+          <t>4.25"</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -31733,7 +31608,7 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>size hidden by folded page corner; time 730</t>
+          <t>size hidden by folded page corner; time 730; size 4.25" per Jesse 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -36956,7 +36831,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>size not legible</t>
+          <t>8.25"</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -36984,7 +36859,7 @@
       </c>
       <c r="K582" t="inlineStr">
         <is>
-          <t>no size written</t>
+          <t>no size written; size 8.25" per Jesse 2026-10-02</t>
         </is>
       </c>
     </row>

--- a/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
+++ b/02-facilities/Cenovus/Lima-OH/USA26046-pig-counts.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crude" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coker" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vac" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acronyms" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-sheet rows" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-invoice 09302026-1" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pigs.xlsx list" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin vs run sheets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crude" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HDS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coker" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vac" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acronyms" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run-sheet rows" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-invoice 09302026-1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pigs.xlsx list" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,7 +747,3427 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D109"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>pigs.xlsx (Sheet1; Sheet2 is identical) - line list with rates. Kept separate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Rate (USD)</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Amount (USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>148.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6" Pin</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>118</v>
+      </c>
+      <c r="D4" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6.25" Pin</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>389.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6.25" Pin</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6.25" Pin</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7.25" Pin</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>548.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8" Pin</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8" BOLTED</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8.25" Pin</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>743.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8.25" BOLTED</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>743.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6.25" Pin</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7.25" Pin</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="D14" t="n">
+        <v>548.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8" Pin</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>8" BOLTED</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>8.25" Pin</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>743.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>8.25" BOLTED</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>743.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6.25" Pin</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1168.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8.5" Swab</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>247.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>148.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>148.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6" Pin</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>118</v>
+      </c>
+      <c r="D24" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6.125" Pin</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>778.8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6.25" Pin</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>778.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>8" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>247.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6" Pin</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>118</v>
+      </c>
+      <c r="D28" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>6" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>148.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6.25" bolt</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>778.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>6.125" Pin</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D31" t="n">
+        <v>389.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8" Pin</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>460.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8" Bolt</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>460.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8" Bolt</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>8.25" Bolt</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1486.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8" Pin</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>8.25" Pin</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1486.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3.75" Pin</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>212.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4" Pin</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>59</v>
+      </c>
+      <c r="D39" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4.125" Pin</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>59</v>
+      </c>
+      <c r="D40" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4'" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D41" t="n">
+        <v>75.59999999999999</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4.125" HR</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" t="n">
+        <v>59</v>
+      </c>
+      <c r="D42" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>8" Pin</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>8.25" Bub</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2028.6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>8" Bub</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="D45" t="n">
+        <v>626.7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>8.5" Swab</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>8.25" Bub</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>676.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D48" t="n">
+        <v>247.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8.5" Swab</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4.25" Pin</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="D50" t="n">
+        <v>259.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>6" Pin</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4</v>
+      </c>
+      <c r="C51" t="n">
+        <v>118</v>
+      </c>
+      <c r="D51" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6.25" Pin</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>519.2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>8" Pin</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>920.4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10" Pin</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>967.6</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>12" Pin</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>826</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>6" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>148.8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>6" Pin</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" t="n">
+        <v>118</v>
+      </c>
+      <c r="D57" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6.25" Pin</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>389.4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>6.25" Bub</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="n">
+        <v>118</v>
+      </c>
+      <c r="D59" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>6" Bub</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>322.2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>6.25" Bub</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>6</v>
+      </c>
+      <c r="C61" t="n">
+        <v>118</v>
+      </c>
+      <c r="D61" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>8" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="D62" t="n">
+        <v>247.8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>8" Pin</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>690.3</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>8.25" Bub</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1352.4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>8.25" Bub</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>6</v>
+      </c>
+      <c r="C65" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1352.4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>8.5" Swab</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>48.3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>10" Swab</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D67" t="n">
+        <v>79.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10" Swab</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3.875" Pin</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4" Pin</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" t="n">
+        <v>59</v>
+      </c>
+      <c r="D70" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4-1/8" HR</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" t="n">
+        <v>59</v>
+      </c>
+      <c r="D71" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4" Pin</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="n">
+        <v>59</v>
+      </c>
+      <c r="D72" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4.125" Pin</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" t="n">
+        <v>59</v>
+      </c>
+      <c r="D73" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>6" Pin</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>118</v>
+      </c>
+      <c r="D74" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8" Pin</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>460.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>10" Pin</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="D76" t="n">
+        <v>967.6</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>12" Pin</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" t="n">
+        <v>826</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4.125" Pin</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="n">
+        <v>59</v>
+      </c>
+      <c r="D78" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2</v>
+      </c>
+      <c r="C79" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D79" t="n">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>6" Pin</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>118</v>
+      </c>
+      <c r="D80" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>6.25" Bub</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>6</v>
+      </c>
+      <c r="C81" t="n">
+        <v>118</v>
+      </c>
+      <c r="D81" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>6.25" Bub</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>6</v>
+      </c>
+      <c r="C82" t="n">
+        <v>118</v>
+      </c>
+      <c r="D82" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>12" Pin</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="n">
+        <v>826</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>10" Pin</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" t="n">
+        <v>483.8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>967.6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>8.25" Pin</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2</v>
+      </c>
+      <c r="C85" t="n">
+        <v>247.8</v>
+      </c>
+      <c r="D85" t="n">
+        <v>495.6</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>6.25" Pin</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2</v>
+      </c>
+      <c r="C86" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D86" t="n">
+        <v>259.6</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>6" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="D87" t="n">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4" Pin</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" t="n">
+        <v>59</v>
+      </c>
+      <c r="D88" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4.125" Pin</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="n">
+        <v>59</v>
+      </c>
+      <c r="D89" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>3" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" t="n">
+        <v>13</v>
+      </c>
+      <c r="D90" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>3.125" Pin</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>106.2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3.25" Pin</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>6</v>
+      </c>
+      <c r="C92" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>247.8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3.3" Pin</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>82.59999999999999</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4" Pin</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="n">
+        <v>59</v>
+      </c>
+      <c r="D94" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4.125" Pin</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" t="n">
+        <v>59</v>
+      </c>
+      <c r="D95" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>8" Pin</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>230.1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>10" Swab</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>3.325" Pin</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>3</v>
+      </c>
+      <c r="C98" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="D98" t="n">
+        <v>123.9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>3.5" Pin</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>6</v>
+      </c>
+      <c r="C99" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D99" t="n">
+        <v>283.2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>3.625" Pin</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>6</v>
+      </c>
+      <c r="C100" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D100" t="n">
+        <v>283.2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3.75" Pin</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C101" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>159.3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>3.75" Pin</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>6</v>
+      </c>
+      <c r="C102" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>318.6</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>3.625" Pin</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>8</v>
+      </c>
+      <c r="C103" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>377.6</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>3.875" Pin</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>4</v>
+      </c>
+      <c r="C104" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>212.4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4'" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="D105" t="n">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>3.625" Pin</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>6</v>
+      </c>
+      <c r="C106" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D106" t="n">
+        <v>283.2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>3.75" Pin</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>3</v>
+      </c>
+      <c r="C107" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>159.3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>3.625" Gauge Foam</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>3</v>
+      </c>
+      <c r="C108" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D108" t="n">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B109" s="5">
+        <f>SUM(B3:B108)</f>
+        <v/>
+      </c>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5">
+        <f>SUM(D3:D108)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Admin pig list (pigs.xlsx) compared with the run-sheet extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Side by side only - neither source is treated as the correct one (Jesse, 2026-10-02). Admin lines are assigned to heaters by matching them, in order, to the service receipts; pigs.xlsx itself carries no heater. Admin cost = its own line amounts (qty x rate, no markup). Run-sheet cost = new pigs only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Heater</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Admin pigs</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Run sheets - all pigs</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Run sheets - new</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Run sheets - used</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Admin cost (USD)</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Run sheets - cost of new (USD)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Difference, admin - run sheets (USD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Crude PR-170028</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>211</v>
+      </c>
+      <c r="C5" t="n">
+        <v>225</v>
+      </c>
+      <c r="D5" t="n">
+        <v>88</v>
+      </c>
+      <c r="E5" t="n">
+        <v>137</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>32429.7</v>
+      </c>
+      <c r="G5" s="4">
+        <f>'Crude'!L30</f>
+        <v/>
+      </c>
+      <c r="H5" s="4">
+        <f>F5-G5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HDS PR-175169</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>1751.2</v>
+      </c>
+      <c r="G6" s="4">
+        <f>'HDS'!L12</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>F6-G6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Coker PR-170002</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>64</v>
+      </c>
+      <c r="C7" t="n">
+        <v>197</v>
+      </c>
+      <c r="D7" t="n">
+        <v>131</v>
+      </c>
+      <c r="E7" t="n">
+        <v>66</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>2763.6</v>
+      </c>
+      <c r="G7" s="4">
+        <f>'Coker'!L47</f>
+        <v/>
+      </c>
+      <c r="H7" s="4">
+        <f>F7-G7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Vac PR-170029</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>88</v>
+      </c>
+      <c r="C8" t="n">
+        <v>148</v>
+      </c>
+      <c r="D8" t="n">
+        <v>79</v>
+      </c>
+      <c r="E8" t="n">
+        <v>69</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>14467.3</v>
+      </c>
+      <c r="G8" s="4">
+        <f>'Vac'!L38</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>F8-G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="5">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="5">
+        <f>SUM(C5:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="5">
+        <f>SUM(D5:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="5">
+        <f>SUM(E5:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="6">
+        <f>SUM(F5:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="6">
+        <f>SUM(G5:G8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="6">
+        <f>SUM(H5:H8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>By heater and size</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Heater</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Admin pigs</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Admin lines (as written)</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Run sheets - all</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Run sheets - new</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Run sheets - used</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Admin minus run-sheet new</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5.8"</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5.875"</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gauge Foam x3, Pin x3, Gauge Foam x3, Gauge Foam x3, Pin x3, Pin x3, Gauge Foam x3, Gauge Foam x3, Pin x3, Bub x3</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F15" t="n">
+        <v>21</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6.125"</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Pin x6, Pin x3</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6.25"</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>63</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pin x3, Pin x9, Pin x9, Pin x9, Pin x9, Pin x6, bolt x6, Pin x3, Bub x3, Bub x6</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>58</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" t="n">
+        <v>38</v>
+      </c>
+      <c r="H17" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6.875"</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7.25"</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Pin x3, Pin x3</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7.75"</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8"</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>43</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pin x3, BOLTED x3, Pin x3, BOLTED x3, Gauge Foam x3, Gauge Foam x3, Pin x2, Bolt x2, Bolt x3, Pin x3, Pin x3, Bub x3, Gauge Foam x3, Gauge Foam x3, Pin x3</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>33</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H21" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>8.25"</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>48</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pin x3, BOLTED x3, Pin x3, BOLTED x3, Bolt x6, Pin x6, Bub x9, Bub x3, Bub x6, Bub x6</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>93</v>
+      </c>
+      <c r="F22" t="n">
+        <v>26</v>
+      </c>
+      <c r="G22" t="n">
+        <v>67</v>
+      </c>
+      <c r="H22" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8.5"</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Swab x3, Swab x3, Swab x3, Swab x3</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Crude</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>10.5"</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>HDS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Gauge Foam x2, Pin x2</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HDS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6.25"</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bub x6, Bub x6</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F26" t="n">
+        <v>11</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>HDS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>6.5"</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3"</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Gauge Foam x3</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3.1"</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3.125"</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pin x3</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3.25"</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pin x6</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" t="n">
+        <v>10</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3.3"</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pin x2</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>27</v>
+      </c>
+      <c r="F32" t="n">
+        <v>20</v>
+      </c>
+      <c r="G32" t="n">
+        <v>7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3.325"</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pin x3</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>3.375"</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>3.5"</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pin x6</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>44</v>
+      </c>
+      <c r="F35" t="n">
+        <v>29</v>
+      </c>
+      <c r="G35" t="n">
+        <v>15</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>3.6"</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>9</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>3.625"</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>23</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pin x6, Pin x8, Pin x6, Gauge Foam x3</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>36</v>
+      </c>
+      <c r="F37" t="n">
+        <v>18</v>
+      </c>
+      <c r="G37" t="n">
+        <v>18</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3.7"</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3.75"</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>12</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pin x3, Pin x6, Pin x3</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>14</v>
+      </c>
+      <c r="F39" t="n">
+        <v>12</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3.8"</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3.875"</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pin x4</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>8</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3.9"</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Gauge Foam x2</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>28</v>
+      </c>
+      <c r="F43" t="n">
+        <v>15</v>
+      </c>
+      <c r="G43" t="n">
+        <v>13</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>6.5"</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Coker</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>84 mm HC</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3.75"</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pin x4</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>3.8"</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>3.875"</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pin x1</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>4"</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>22</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pin x8, Gauge Foam x4, Pin x2, Pin x4, Pin x2, Pin x2</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>20</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14</v>
+      </c>
+      <c r="G49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>4.1"</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4.125"</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>15</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pin x2, HR x3, HR x2, Pin x2, Pin x2, Pin x2, Pin x2</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>10</v>
+      </c>
+      <c r="F51" t="n">
+        <v>7</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>4.25"</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pin x4</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>30</v>
+      </c>
+      <c r="F52" t="n">
+        <v>16</v>
+      </c>
+      <c r="G52" t="n">
+        <v>14</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5.75"</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5.8"</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>6"</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>10</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pin x4, Pin x4, Gauge Foam x2</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="n">
+        <v>13</v>
+      </c>
+      <c r="G55" t="n">
+        <v>11</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>6.25"</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>6</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pin x4, Pin x2</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>12</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="n">
+        <v>10</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>8"</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pin x4, Pin x2, Pin x1</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>8.25"</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pin x2</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" t="n">
+        <v>5</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>10"</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>11</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pin x2, Swab x3, Swab x1, Pin x2, Pin x2, Swab x1</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>14</v>
+      </c>
+      <c r="F59" t="n">
+        <v>7</v>
+      </c>
+      <c r="G59" t="n">
+        <v>7</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>10.25"</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12"</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>6</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pin x2, Pin x2, Pin x2</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>10</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="n">
+        <v>8</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Vac</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>12.25"</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Observed, not concluded: admin lines 5-10 and 11-16 are identical (the receipt 8403 set: 6.25" x9, 7.25" x3, 8" x3, 8" bolted x3, 8.25" x3, 8.25" bolted x3), and receipt 8403 itself lists 7.75", not 7.25". "Bub" appears only on the admin list, never on the run sheets or receipts.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A64:H64"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2113,7 +5534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2670,7 +6091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4802,7 +8223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6529,7 +9950,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6715,7 +10136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36868,7 +40289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37797,1765 +41218,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D109"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>pigs.xlsx (Sheet1; Sheet2 is identical) - line list with rates. Kept separate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Qty</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Rate (USD)</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Amount (USD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>6" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>148.8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6" Pin</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>118</v>
-      </c>
-      <c r="D4" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>6.25" Pin</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>389.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6.25" Pin</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C6" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1168.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6.25" Pin</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1168.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>7.25" Pin</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="D8" t="n">
-        <v>548.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8" Pin</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>690.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>8" BOLTED</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>690.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>8.25" Pin</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="D11" t="n">
-        <v>743.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>8.25" BOLTED</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>743.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>6.25" Pin</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>9</v>
-      </c>
-      <c r="C13" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1168.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>7.25" Pin</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>548.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>8" Pin</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>690.3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>8" BOLTED</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>690.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>8.25" Pin</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C17" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="D17" t="n">
-        <v>743.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>8.25" BOLTED</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>743.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6.25" Pin</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>9</v>
-      </c>
-      <c r="C19" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1168.2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>8.5" Swab</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>48.3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>8" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C21" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="D21" t="n">
-        <v>247.8</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>6" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>148.8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="D23" t="n">
-        <v>148.8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6" Pin</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" t="n">
-        <v>118</v>
-      </c>
-      <c r="D24" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>6.125" Pin</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>6</v>
-      </c>
-      <c r="C25" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D25" t="n">
-        <v>778.8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>6.25" Pin</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D26" t="n">
-        <v>778.8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>8" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="D27" t="n">
-        <v>247.8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>6" Pin</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" t="n">
-        <v>118</v>
-      </c>
-      <c r="D28" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>6" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="D29" t="n">
-        <v>148.8</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>6.25" bolt</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>6</v>
-      </c>
-      <c r="C30" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D30" t="n">
-        <v>778.8</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>6.125" Pin</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C31" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D31" t="n">
-        <v>389.4</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>8" Pin</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>2</v>
-      </c>
-      <c r="C32" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D32" t="n">
-        <v>460.2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>8" Bolt</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>2</v>
-      </c>
-      <c r="C33" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D33" t="n">
-        <v>460.2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>8" Bolt</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>690.3</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>8.25" Bolt</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>6</v>
-      </c>
-      <c r="C35" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1486.8</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>8" Pin</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>690.3</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>8.25" Pin</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>6</v>
-      </c>
-      <c r="C37" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1486.8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>3.75" Pin</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>4</v>
-      </c>
-      <c r="C38" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>212.4</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>4" Pin</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>8</v>
-      </c>
-      <c r="C39" t="n">
-        <v>59</v>
-      </c>
-      <c r="D39" t="n">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>4.125" Pin</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" t="n">
-        <v>59</v>
-      </c>
-      <c r="D40" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>4'" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="D41" t="n">
-        <v>75.59999999999999</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>4.125" HR</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" t="n">
-        <v>59</v>
-      </c>
-      <c r="D42" t="n">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>8" Pin</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>3</v>
-      </c>
-      <c r="C43" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>690.3</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>8.25" Bub</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>9</v>
-      </c>
-      <c r="C44" t="n">
-        <v>225.4</v>
-      </c>
-      <c r="D44" t="n">
-        <v>2028.6</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>8" Bub</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" t="n">
-        <v>208.9</v>
-      </c>
-      <c r="D45" t="n">
-        <v>626.7</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>8.5" Swab</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>3</v>
-      </c>
-      <c r="C46" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="D46" t="n">
-        <v>48.3</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>8.25" Bub</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" t="n">
-        <v>225.4</v>
-      </c>
-      <c r="D47" t="n">
-        <v>676.2</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>8" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="D48" t="n">
-        <v>247.8</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>8.5" Swab</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>3</v>
-      </c>
-      <c r="C49" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="D49" t="n">
-        <v>48.3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>4.25" Pin</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>4</v>
-      </c>
-      <c r="C50" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="D50" t="n">
-        <v>259.6</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>6" Pin</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>4</v>
-      </c>
-      <c r="C51" t="n">
-        <v>118</v>
-      </c>
-      <c r="D51" t="n">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>6.25" Pin</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>4</v>
-      </c>
-      <c r="C52" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D52" t="n">
-        <v>519.2</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>8" Pin</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>4</v>
-      </c>
-      <c r="C53" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D53" t="n">
-        <v>920.4</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>10" Pin</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" t="n">
-        <v>483.8</v>
-      </c>
-      <c r="D54" t="n">
-        <v>967.6</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>12" Pin</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" t="n">
-        <v>826</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1652</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>6" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>3</v>
-      </c>
-      <c r="C56" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="D56" t="n">
-        <v>148.8</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>6" Pin</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" t="n">
-        <v>118</v>
-      </c>
-      <c r="D57" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>6.25" Pin</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>3</v>
-      </c>
-      <c r="C58" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D58" t="n">
-        <v>389.4</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>6.25" Bub</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>3</v>
-      </c>
-      <c r="C59" t="n">
-        <v>118</v>
-      </c>
-      <c r="D59" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>6" Bub</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>3</v>
-      </c>
-      <c r="C60" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="D60" t="n">
-        <v>322.2</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>6.25" Bub</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>6</v>
-      </c>
-      <c r="C61" t="n">
-        <v>118</v>
-      </c>
-      <c r="D61" t="n">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>8" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="D62" t="n">
-        <v>247.8</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>8" Pin</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D63" t="n">
-        <v>690.3</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>8.25" Bub</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>6</v>
-      </c>
-      <c r="C64" t="n">
-        <v>225.4</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1352.4</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>8.25" Bub</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>6</v>
-      </c>
-      <c r="C65" t="n">
-        <v>225.4</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1352.4</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>8.5" Swab</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>3</v>
-      </c>
-      <c r="C66" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="D66" t="n">
-        <v>48.3</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>10" Swab</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>3</v>
-      </c>
-      <c r="C67" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="D67" t="n">
-        <v>79.5</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>10" Swab</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="D68" t="n">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>3.875" Pin</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D69" t="n">
-        <v>53.1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>4" Pin</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>2</v>
-      </c>
-      <c r="C70" t="n">
-        <v>59</v>
-      </c>
-      <c r="D70" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>4-1/8" HR</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>2</v>
-      </c>
-      <c r="C71" t="n">
-        <v>59</v>
-      </c>
-      <c r="D71" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>4" Pin</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>4</v>
-      </c>
-      <c r="C72" t="n">
-        <v>59</v>
-      </c>
-      <c r="D72" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>4.125" Pin</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>2</v>
-      </c>
-      <c r="C73" t="n">
-        <v>59</v>
-      </c>
-      <c r="D73" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>6" Pin</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>4</v>
-      </c>
-      <c r="C74" t="n">
-        <v>118</v>
-      </c>
-      <c r="D74" t="n">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>8" Pin</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>2</v>
-      </c>
-      <c r="C75" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D75" t="n">
-        <v>460.2</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>10" Pin</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C76" t="n">
-        <v>483.8</v>
-      </c>
-      <c r="D76" t="n">
-        <v>967.6</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>12" Pin</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>2</v>
-      </c>
-      <c r="C77" t="n">
-        <v>826</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1652</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>4.125" Pin</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>2</v>
-      </c>
-      <c r="C78" t="n">
-        <v>59</v>
-      </c>
-      <c r="D78" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>6" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>2</v>
-      </c>
-      <c r="C79" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="D79" t="n">
-        <v>99.2</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>6" Pin</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>2</v>
-      </c>
-      <c r="C80" t="n">
-        <v>118</v>
-      </c>
-      <c r="D80" t="n">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>6.25" Bub</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>6</v>
-      </c>
-      <c r="C81" t="n">
-        <v>118</v>
-      </c>
-      <c r="D81" t="n">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>6.25" Bub</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>6</v>
-      </c>
-      <c r="C82" t="n">
-        <v>118</v>
-      </c>
-      <c r="D82" t="n">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>12" Pin</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>2</v>
-      </c>
-      <c r="C83" t="n">
-        <v>826</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1652</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>10" Pin</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>2</v>
-      </c>
-      <c r="C84" t="n">
-        <v>483.8</v>
-      </c>
-      <c r="D84" t="n">
-        <v>967.6</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>8.25" Pin</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>2</v>
-      </c>
-      <c r="C85" t="n">
-        <v>247.8</v>
-      </c>
-      <c r="D85" t="n">
-        <v>495.6</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>6.25" Pin</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>2</v>
-      </c>
-      <c r="C86" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="D86" t="n">
-        <v>259.6</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>6" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>2</v>
-      </c>
-      <c r="C87" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="D87" t="n">
-        <v>99.2</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>4" Pin</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>2</v>
-      </c>
-      <c r="C88" t="n">
-        <v>59</v>
-      </c>
-      <c r="D88" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>4.125" Pin</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>2</v>
-      </c>
-      <c r="C89" t="n">
-        <v>59</v>
-      </c>
-      <c r="D89" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>3" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>3</v>
-      </c>
-      <c r="C90" t="n">
-        <v>13</v>
-      </c>
-      <c r="D90" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>3.125" Pin</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>3</v>
-      </c>
-      <c r="C91" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="D91" t="n">
-        <v>106.2</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>3.25" Pin</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>6</v>
-      </c>
-      <c r="C92" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="D92" t="n">
-        <v>247.8</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>3.3" Pin</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>2</v>
-      </c>
-      <c r="C93" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="D93" t="n">
-        <v>82.59999999999999</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>4" Pin</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>2</v>
-      </c>
-      <c r="C94" t="n">
-        <v>59</v>
-      </c>
-      <c r="D94" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>4.125" Pin</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>2</v>
-      </c>
-      <c r="C95" t="n">
-        <v>59</v>
-      </c>
-      <c r="D95" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>8" Pin</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D96" t="n">
-        <v>230.1</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>10" Swab</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="D97" t="n">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>3.325" Pin</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>3</v>
-      </c>
-      <c r="C98" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="D98" t="n">
-        <v>123.9</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>3.5" Pin</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>6</v>
-      </c>
-      <c r="C99" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="D99" t="n">
-        <v>283.2</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>3.625" Pin</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>6</v>
-      </c>
-      <c r="C100" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="D100" t="n">
-        <v>283.2</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>3.75" Pin</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>3</v>
-      </c>
-      <c r="C101" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D101" t="n">
-        <v>159.3</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>3.75" Pin</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>6</v>
-      </c>
-      <c r="C102" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D102" t="n">
-        <v>318.6</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>3.625" Pin</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>8</v>
-      </c>
-      <c r="C103" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="D103" t="n">
-        <v>377.6</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>3.875" Pin</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>4</v>
-      </c>
-      <c r="C104" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D104" t="n">
-        <v>212.4</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>4'" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>2</v>
-      </c>
-      <c r="C105" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="D105" t="n">
-        <v>37.8</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>3.625" Pin</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>6</v>
-      </c>
-      <c r="C106" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="D106" t="n">
-        <v>283.2</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>3.75" Pin</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>3</v>
-      </c>
-      <c r="C107" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="D107" t="n">
-        <v>159.3</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>3.625" Gauge Foam</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>3</v>
-      </c>
-      <c r="C108" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="D108" t="n">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B109" s="5">
-        <f>SUM(B3:B108)</f>
-        <v/>
-      </c>
-      <c r="C109" s="5" t="n"/>
-      <c r="D109" s="5">
-        <f>SUM(D3:D108)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>